--- a/dealer & retailer data.xlsx
+++ b/dealer & retailer data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ajitverma/Documents/order_dispatch_tracking_system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D473AF5-757B-5246-86E6-00C810B60247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C550FA8C-D3F9-0C4C-A12E-7EB46A087177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17280" activeTab="1" xr2:uid="{E5C52BC3-1A62-4958-924B-B2E44922EF19}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2922" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2959" uniqueCount="531">
   <si>
     <t>Sold-To Code</t>
   </si>
@@ -1536,6 +1536,105 @@
   </si>
   <si>
     <t>Type of user login names</t>
+  </si>
+  <si>
+    <t>SELECT * FROM odts.users;</t>
+  </si>
+  <si>
+    <t>INSERT INTO odts.users (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    user_role_id, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dealer_id, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    user_name, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    user_login_name, </t>
+  </si>
+  <si>
+    <t>password_hash,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    user_phone, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    user_email</t>
+  </si>
+  <si>
+    <t>)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ur.role_id,</t>
+  </si>
+  <si>
+    <t>d.dealer_id,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    d.dealer_name,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    CASE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        WHEN rn BETWEEN 1 AND 20 THEN 'alpha' || rn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        WHEN rn BETWEEN 21 AND 40 THEN 'beta' || rn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        WHEN rn BETWEEN 41 AND 60 THEN 'gamma' || rn</t>
+  </si>
+  <si>
+    <t>WHEN rn BETWEEN 61 AND 80 THEN 'delta' || rn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    END,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crypt( CASE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    END, gen_salt('bf')),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    d.dealer_phone,</t>
+  </si>
+  <si>
+    <t>d.dealer_email</t>
+  </si>
+  <si>
+    <t>FROM (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    SELECT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        d.*, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        ROW_NUMBER() OVER (ORDER BY d.dealer_id) AS rn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    FROM odts.dealers d</t>
+  </si>
+  <si>
+    <t>) d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOIN odts.user_roles ur </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ON ur.role_name = 'DEALER';</t>
+  </si>
+  <si>
+    <t>select * from odts.users;</t>
   </si>
 </sst>
 </file>
@@ -1703,7 +1802,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1748,9 +1847,8 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2085,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A543527-1AAA-46D9-818C-0833CBD13630}">
-  <dimension ref="A1:I322"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
@@ -2094,12 +2192,11 @@
     <col min="4" max="4" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" style="17"/>
-    <col min="8" max="8" width="19.1640625" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.83203125" style="2"/>
+    <col min="7" max="7" width="19.1640625" style="16" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="3" customFormat="1" ht="26" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2118,12 +2215,11 @@
       <c r="F1" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="3" t="s">
+      <c r="G1" s="14" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>9110032672</v>
       </c>
@@ -2143,15 +2239,14 @@
         <f>_xlfn.CONCAT("Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '",A2,"','",B2,"','",C2,"',",D2,",'",E2,"',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);")</f>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110032672','ADESH TRADERS','VARANASI',9415204148,'ANAND GUPTA',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>476</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>9110097794</v>
       </c>
@@ -2171,15 +2266,14 @@
         <f t="shared" ref="F3:F66" si="0">_xlfn.CONCAT("Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '",A3,"','",B3,"','",C3,"',",D3,",'",E3,"',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);")</f>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110097794','AJAY PAINT AND HARDWARE STORES','VARANASI',9450872462,'HIMANSHU AGRAHARI',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="18" t="s">
+      <c r="G3" s="17" t="s">
         <v>477</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>9110033143</v>
       </c>
@@ -2199,15 +2293,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110033143','AKASH ENTERPRISES','VARANASI',9415202341,'SHUBHASH JAISWAL',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="18" t="s">
+      <c r="G4" s="17" t="s">
         <v>478</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>9110117683</v>
       </c>
@@ -2227,15 +2320,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110117683','AKK TRADERS','VARANASI',7860091091,'Ashwani Kumar Khanna',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="18" t="s">
+      <c r="G5" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>9110235610</v>
       </c>
@@ -2255,15 +2347,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110235610','AMAN BUILDING MATERIALS','VARANASI',9450251409,'RAMASHREY SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="18" t="s">
+      <c r="G6" s="17" t="s">
         <v>480</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>9110221017</v>
       </c>
@@ -2283,15 +2374,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110221017','AMAR CONSTRUCTIONS AND SUPPLIER','VARANASI',9336835074,'SUNIL KUMAR',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="18" t="s">
+      <c r="G7" s="17" t="s">
         <v>481</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>9110033203</v>
       </c>
@@ -2311,15 +2401,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110033203','ANJALI ENTERPRISES','VARANASI',9415336241,'ANIL KUMAR SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="18" t="s">
+      <c r="G8" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="H8" s="6" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>9110202061</v>
       </c>
@@ -2339,15 +2428,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110202061','ANKIT BUILDING MATERIALS','VARANASI',9453397468,'ABHAY KUMAR SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="18" t="s">
+      <c r="G9" s="17" t="s">
         <v>483</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9110208385</v>
       </c>
@@ -2367,15 +2455,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110208385','ANUJ TRADING COMPANY','VARANASI',8052212829,'SIMPAL KESHARI',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="18" t="s">
+      <c r="G10" s="17" t="s">
         <v>484</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>9110207934</v>
       </c>
@@ -2395,15 +2482,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110207934','AWANTI CEMENT AGENCY','VARANASI',8887652664,'RAJENDRA NATH GUPTA',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="18" t="s">
+      <c r="G11" s="17" t="s">
         <v>485</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>9110217758</v>
       </c>
@@ -2423,15 +2509,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110217758','AYUSH TRADING COMPANY','VARANASI',9451609946,'HARIDASH JAISHAWAL',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="18" t="s">
+      <c r="G12" s="17" t="s">
         <v>486</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>9110235576</v>
       </c>
@@ -2451,15 +2536,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110235576','BEMISHAL CEMENT AGENCY','VARANASI',8318590576,'MOHAMMAD SALMAN',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="18" t="s">
+      <c r="G13" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="H13" s="6" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>9110232851</v>
       </c>
@@ -2479,15 +2563,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110232851','BHAGIRATHI CONSTRUCTION AND SUPPLIE','VARANASI',9044339800,'LALLAN SHARMA',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="18" t="s">
+      <c r="G14" s="17" t="s">
         <v>488</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9110092659</v>
       </c>
@@ -2507,15 +2590,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110092659','BHOLE NATH ENTERPRISES','VARANASI',9454231797,'Dilip Kumar Rai',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="18" t="s">
+      <c r="G15" s="17" t="s">
         <v>489</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="H15" s="6" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>9110033101</v>
       </c>
@@ -2535,15 +2617,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110033101','BIRASAN ENTERPRISES','VARANASI',9415223227,'Sanjay Ghosh',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="18" t="s">
+      <c r="G16" s="17" t="s">
         <v>490</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="H16" s="6" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>9110187050</v>
       </c>
@@ -2563,15 +2644,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110187050','DAYAL TRADERS','VARANASI',9919156255,'SANTOSH KUMAR GUPTA',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="18" t="s">
+      <c r="G17" s="17" t="s">
         <v>491</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="H17" s="6" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>9110131504</v>
       </c>
@@ -2591,15 +2671,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110131504','DEVARSHI ENTERPRISES','VARANASI',7754994433,'Ramesh Pratap Singh',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="18" t="s">
+      <c r="G18" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>9110204851</v>
       </c>
@@ -2619,15 +2698,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110204851','DIVYANSH BUILDING MATERIAL','VARANASI',9795337722,'ROSHAN YADAV',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="18" t="s">
+      <c r="G19" s="17" t="s">
         <v>493</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>9110209421</v>
       </c>
@@ -2647,15 +2725,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110209421','FVS TRADING CORPORATION','VARANASI',9125461413,'ARSHAD ANSARI',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="18" t="s">
+      <c r="G20" s="17" t="s">
         <v>494</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="H20" s="6" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>9110144134</v>
       </c>
@@ -2675,15 +2752,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110144134','G S TRADERS','VARANASI',9415696821,'GHANSHYAM YADAV',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="18" t="s">
+      <c r="G21" s="17" t="s">
         <v>495</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>9110184692</v>
       </c>
@@ -2703,15 +2779,14 @@
         <f t="shared" si="0"/>
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110184692','GEETA BUILDING MATERIAL','VARANASI',9839144542,'NAND',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="18" t="s">
+      <c r="G22" s="17" t="s">
         <v>496</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4">
         <v>9110178852</v>
       </c>
@@ -2732,11 +2807,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110178852','HARSH CEMENT AGENCY','VARANASI',9838674727,'PANKAJ KUMAR DUBEY',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G23" s="15"/>
-      <c r="I23" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A24" s="4">
         <v>9110173220</v>
       </c>
@@ -2757,11 +2832,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110173220','HEMANT ENTERPRISES','VARANASI',9415980801,'OM PRAKASH CHAURASIA',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G24" s="15"/>
-      <c r="I24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A25" s="4">
         <v>9110206595</v>
       </c>
@@ -2782,11 +2857,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110206595','JAY AMBEY ENTERPRISES','VARANASI',9451137695,'SANI KUMAR CHAURASIYA',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G25" s="15"/>
-      <c r="I25" s="6" t="s">
+      <c r="H25" s="6" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A26" s="4">
         <v>9110202060</v>
       </c>
@@ -2807,11 +2882,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110202060','JYOTI BUILDING MATERIALS','VARANASI',8115332151,'JYOTI BHUSHAN SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G26" s="15"/>
-      <c r="I26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A27" s="4">
         <v>9110171676</v>
       </c>
@@ -2832,11 +2907,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110171676','KAMAL ENTERPRISES','VARANASI',7007810004,'RATNESH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G27" s="15"/>
-      <c r="I27" s="6" t="s">
+      <c r="H27" s="6" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A28" s="4">
         <v>9110236010</v>
       </c>
@@ -2857,11 +2932,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110236010','KESHARWANI AGENCIES','VARANASI',9415619899,'RAVI SHANKER KESARI',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G28" s="15"/>
-      <c r="I28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A29" s="4">
         <v>9110170402</v>
       </c>
@@ -2882,11 +2957,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110170402','KOMAL ENTERPRISES','VARANASI',7376746105,'AMIT',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G29" s="15"/>
-      <c r="I29" s="6" t="s">
+      <c r="H29" s="6" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4">
         <v>9110045030</v>
       </c>
@@ -2907,11 +2982,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110045030','KRIPA SHANKAR SINGH','VARANASI',9415300220,'Balkeshwar Prasad Singh',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G30" s="15"/>
-      <c r="I30" s="6" t="s">
+      <c r="H30" s="6" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A31" s="4">
         <v>9110225636</v>
       </c>
@@ -2932,11 +3007,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110225636','KRIPA TRADERS','VARANASI',9120292964,'PRAJJWAL CHAUBEY',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G31" s="15"/>
-      <c r="I31" s="6" t="s">
+      <c r="H31" s="6" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A32" s="4">
         <v>9110205222</v>
       </c>
@@ -2957,11 +3032,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110205222','KRISHNA ENTERPRISES','VARANASI',9219785608,'NRIPENDRA SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G32" s="15"/>
-      <c r="I32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A33" s="4">
         <v>9110203758</v>
       </c>
@@ -2982,11 +3057,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110203758','KRV ENTERPRISES','VARANASI',9717082620,'SUREKHA DEVI',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G33" s="15"/>
-      <c r="I33" s="6" t="s">
+      <c r="H33" s="6" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A34" s="4">
         <v>9110234954</v>
       </c>
@@ -3007,11 +3082,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110234954','M K ENTERPRISES','VARANASI',9695795004,'MANOJ KUMAR',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G34" s="15"/>
-      <c r="I34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A35" s="4">
         <v>9110190952</v>
       </c>
@@ -3032,11 +3107,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110190952','MAA VAISHNO ENTERPRISES','VARANASI',9450330719,'ANIL KUMAR',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G35" s="15"/>
-      <c r="I35" s="6" t="s">
+      <c r="H35" s="6" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A36" s="4">
         <v>9110172831</v>
       </c>
@@ -3057,11 +3132,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110172831','MAA VASHINO HARDWARE BUILDING','VARANASI',9918777813,'GURU',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G36" s="15"/>
-      <c r="I36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4">
         <v>9110130915</v>
       </c>
@@ -3082,11 +3157,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110130915','MAHARAJ JI BUILDING MATERIAL','VARANASI',9839903666,'KRISHNA AVATAR',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G37" s="15"/>
-      <c r="I37" s="6" t="s">
+      <c r="H37" s="6" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A38" s="4">
         <v>9110187741</v>
       </c>
@@ -3107,11 +3182,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110187741','MAHAVEER ENTERPRISES','VARANASI',9695004001,'PANKAJ KUMAR SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G38" s="15"/>
-      <c r="I38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A39" s="4">
         <v>9110092656</v>
       </c>
@@ -3132,11 +3207,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110092656','MALTI BUILDING MATERIAL','VARANASI',9839519855,'Chote Lal Pathak',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G39" s="15"/>
-      <c r="I39" s="6" t="s">
+      <c r="H39" s="6" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A40" s="4">
         <v>9110208384</v>
       </c>
@@ -3157,11 +3232,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110208384','MATICOTECH INFRASTRUCTURE PVT LTD','VARANASI',8707339385,'SHIKHA SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G40" s="15"/>
-      <c r="I40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A41" s="4">
         <v>9110217209</v>
       </c>
@@ -3182,11 +3257,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110217209','MISHRA BUILDING SOLUTIONS','VARANASI',7007599046,'PRAVINA DEVI',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G41" s="15"/>
-      <c r="I41" s="6" t="s">
+      <c r="H41" s="6" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A42" s="4">
         <v>9110231172</v>
       </c>
@@ -3207,11 +3282,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110231172','MOURYA ENTERRPISES','VARANASI',7524936871,'NANDLAL MAURYA',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G42" s="15"/>
-      <c r="I42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A43" s="4">
         <v>9110228566</v>
       </c>
@@ -3232,11 +3307,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110228566','NEW PRADEEP STEELS','VARANASI',9839093699,'PRADIP KUMAR',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G43" s="15"/>
-      <c r="I43" s="6" t="s">
+      <c r="H43" s="6" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4">
         <v>9110200556</v>
       </c>
@@ -3257,11 +3332,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110200556','OM BUILDING MATERIAL','VARANASI',9919568696,'MUKESH YADAV',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G44" s="15"/>
-      <c r="I44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A45" s="4">
         <v>9110170948</v>
       </c>
@@ -3282,11 +3357,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110170948','OM SHIV BHOLE BUILDING MATERIAL','VARANASI',8840542177,'RITU TIWARI',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G45" s="15"/>
-      <c r="I45" s="6" t="s">
+      <c r="H45" s="6" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A46" s="4">
         <v>9110234216</v>
       </c>
@@ -3307,11 +3382,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110234216','OM SHREE SAI NATH ENTERPRISES','VARANASI',9919781361,'MUHAMMAD SALIM',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G46" s="15"/>
-      <c r="I46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A47" s="4">
         <v>9110033198</v>
       </c>
@@ -3332,11 +3407,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110033198','OM TRADERS','VARANASI',9451582416,'Shiv Bhajan Pandey',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G47" s="15"/>
-      <c r="I47" s="6" t="s">
+      <c r="H47" s="6" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A48" s="4">
         <v>9110220921</v>
       </c>
@@ -3357,11 +3432,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110220921','PARTH BUILDCON','VARANASI',9611375476,'ANJESH KUMAR TRIPATHI',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G48" s="15"/>
-      <c r="I48" s="6" t="s">
+      <c r="H48" s="6" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A49" s="4">
         <v>9110178792</v>
       </c>
@@ -3382,11 +3457,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110178792','PATHAK BUILDING MATERIALS','VARANASI',9839505929,'PRADEEP KUMAR',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G49" s="15"/>
-      <c r="I49" s="6" t="s">
+      <c r="H49" s="6" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A50" s="4">
         <v>9110237589</v>
       </c>
@@ -3407,11 +3482,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110237589','PAWAN ENTERPRISES','VARANASI',8090412525,'PAWAN KUMAR CHOUBEY',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G50" s="15"/>
-      <c r="I50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4">
         <v>9110046614</v>
       </c>
@@ -3432,11 +3507,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110046614','PURWAR CEMENT BHANDAR','VARANASI',9415305397,'ADITYA GUPTA',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G51" s="15"/>
-      <c r="I51" s="6" t="s">
+      <c r="H51" s="6" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A52" s="4">
         <v>9110033210</v>
       </c>
@@ -3457,11 +3532,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110033210','R K BUILDING MATERIAL','VARANASI',9415343325,'RISHIKESH SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G52" s="15"/>
-      <c r="I52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A53" s="4">
         <v>9110225594</v>
       </c>
@@ -3482,11 +3557,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110225594','RAGINI ENTERPRISES','VARANASI',9088666333,'RAGINI SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G53" s="15"/>
-      <c r="I53" s="6" t="s">
+      <c r="H53" s="6" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A54" s="4">
         <v>9110070000</v>
       </c>
@@ -3507,11 +3582,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110070000','RAJARAM OMPRAKASH IRON STORE','VARANASI',9956585951,'OM PRAKASH GUPTA',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G54" s="15"/>
-      <c r="I54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A55" s="4">
         <v>9110033157</v>
       </c>
@@ -3532,11 +3607,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110033157','ROSHAN CEMENT AGENCY','VARANASI',9415304457,'UMESH KUMAR',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G55" s="15"/>
-      <c r="I55" s="6" t="s">
+      <c r="H55" s="6" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A56" s="4">
         <v>9110235599</v>
       </c>
@@ -3557,11 +3632,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110235599','ROYAL TRADERS','VARANASI',8318617656,'WASEEM AKHTAR',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G56" s="15"/>
-      <c r="I56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A57" s="4">
         <v>9110180027</v>
       </c>
@@ -3582,11 +3657,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110180027','S K ENTERPRISES','VARANASI',9919010488,'SATISH KUMAR SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G57" s="15"/>
-      <c r="I57" s="6" t="s">
+      <c r="H57" s="6" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A58" s="4">
         <v>9110206768</v>
       </c>
@@ -3607,11 +3682,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110206768','SAHU TRADERS','VARANASI',7905825188,'SHWETA GUPTA',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G58" s="15"/>
-      <c r="I58" s="6" t="s">
+      <c r="H58" s="6" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A59" s="4">
         <v>9110093690</v>
       </c>
@@ -3632,11 +3707,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110093690','SAI CEMENT AGENCY','VARANASI',9453203994,'Tribhuvan Mishra',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G59" s="15"/>
-      <c r="I59" s="6" t="s">
+      <c r="H59" s="6" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A60" s="4">
         <v>9110078716</v>
       </c>
@@ -3657,11 +3732,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110078716','SAMRAT IRON STORES','VARANASI',9415285959,'Shyam Sundar Singh Kashyap',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G60" s="15"/>
-      <c r="I60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A61" s="4">
         <v>9110033156</v>
       </c>
@@ -3682,11 +3757,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110033156','SATYA NARAIN CEMENT AGENCY','VARANASI',9839910609,'Shyam Narain Singh',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G61" s="15"/>
-      <c r="I61" s="6" t="s">
+      <c r="H61" s="6" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A62" s="4">
         <v>9110033205</v>
       </c>
@@ -3707,11 +3782,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110033205','SHIVA CEMENT AGENCY','VARANASI',9415988037,'Dhirendra Kumar Yadav',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G62" s="15"/>
-      <c r="I62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A63" s="4">
         <v>9110033207</v>
       </c>
@@ -3732,11 +3807,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110033207','SHIVAM CEMENT AGENCY','VARANASI',9415446150,'RAJESH KUMAR',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G63" s="15"/>
-      <c r="I63" s="6" t="s">
+      <c r="H63" s="6" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A64" s="4">
         <v>9110159541</v>
       </c>
@@ -3757,11 +3832,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110159541','SHREE BALAJI ENTERPRISES','VARANASI',9336182012,'NANDINI SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G64" s="15"/>
-      <c r="I64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="65" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A65" s="4">
         <v>9110235580</v>
       </c>
@@ -3782,11 +3857,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110235580','SHREE MAHADEV BUILDING MATERIAL','VARANASI',7785804546,'RAJAT SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G65" s="15"/>
-      <c r="I65" s="6" t="s">
+      <c r="H65" s="6" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A66" s="4">
         <v>9110033213</v>
       </c>
@@ -3807,11 +3882,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110033213','SHREE RAM IRON STORES','VARANASI',9415447483,'BRIJESH KUMAR VARMAN',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G66" s="15"/>
-      <c r="I66" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="67" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A67" s="4">
         <v>9110206767</v>
       </c>
@@ -3832,11 +3907,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110206767','SHREE RAM STEEL','VARANASI',6392041429,'ASHOK SETH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G67" s="15"/>
-      <c r="I67" s="6" t="s">
+      <c r="H67" s="6" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="68" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A68" s="4">
         <v>9110234300</v>
       </c>
@@ -3857,11 +3932,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110234300','SHRI GANPATI INFRATECH','VARANASI',7376590900,'PRATIBHA TIWARI',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G68" s="15"/>
-      <c r="I68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="69" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A69" s="4">
         <v>9110224954</v>
       </c>
@@ -3882,11 +3957,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110224954','SHRI RAM ENTERPRISES','VARANASI',7071973919,'AYUSH JAISWAL',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G69" s="15"/>
-      <c r="I69" s="6" t="s">
+      <c r="H69" s="6" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="70" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A70" s="4">
         <v>9110183722</v>
       </c>
@@ -3907,11 +3982,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110183722','SHRI SIDDHI VINAYAK BUILDING','VARANASI',6394817496,'JAY',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G70" s="15"/>
-      <c r="I70" s="6" t="s">
+      <c r="H70" s="6" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="71" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A71" s="4">
         <v>9110235624</v>
       </c>
@@ -3932,11 +4007,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110235624','SINGH BROTHERS','VARANASI',9838808962,'ANIL KUMAR SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G71" s="15"/>
-      <c r="I71" s="6" t="s">
+      <c r="H71" s="6" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="72" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A72" s="4">
         <v>9110220933</v>
       </c>
@@ -3957,11 +4032,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110220933','SN INFRA MARKET','VARANASI',7905258004,'AMIT UPADHYAY',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G72" s="15"/>
-      <c r="I72" s="6" t="s">
+      <c r="H72" s="6" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="73" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A73" s="4">
         <v>9110228028</v>
       </c>
@@ -3982,11 +4057,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110228028','SRI MAHADEV ENTERPRISES','VARANASI',8574508918,'VIJAY BAHADUR SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G73" s="15"/>
-      <c r="I73" s="6" t="s">
+      <c r="H73" s="6" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="74" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A74" s="4">
         <v>9110166533</v>
       </c>
@@ -4007,11 +4082,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110166533','SUMITRA TRADERS','VARANASI',8318581393,'SUMITRA DEVI',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G74" s="15"/>
-      <c r="I74" s="6" t="s">
+      <c r="H74" s="6" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="75" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A75" s="4">
         <v>9110068757</v>
       </c>
@@ -4032,11 +4107,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110068757','SUNDER CEMENT AGENCY','VARANASI',7905926492,'SURENDRA KUMAR YADAV',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G75" s="15"/>
-      <c r="I75" s="6" t="s">
+      <c r="H75" s="6" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="76" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A76" s="4">
         <v>9110188732</v>
       </c>
@@ -4057,11 +4132,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110188732','VIDHYA ENTERPRISES','VARANASI',9559895003,'MAHENDRA PRATAP SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G76" s="15"/>
-      <c r="I76" s="6" t="s">
+      <c r="H76" s="6" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="77" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A77" s="4">
         <v>9110162175</v>
       </c>
@@ -4082,11 +4157,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110162175','VIJAY SHANKAR CONSTRUCTION','VARANASI',9935262692,'VIJAY SHANKAR',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G77" s="15"/>
-      <c r="I77" s="6" t="s">
+      <c r="H77" s="6" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="78" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A78" s="4">
         <v>9110145353</v>
       </c>
@@ -4107,11 +4182,11 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110145353','VINAY BUILDING MATERIALS','VARANASI',9450012613,'RANJEET SINGH',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G78" s="15"/>
-      <c r="I78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="79" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A79" s="4">
         <v>9110033145</v>
       </c>
@@ -4132,18 +4207,18 @@
         <v>Insert into odts.dealers (dealer_code, dealer_company_name, dealer_address, dealer_phone, dealer_name,  created_by, created_at, updated_by, updated_at) values ( '9110033145','VISHWANATH PRASAD SATYA CHARAN','VARANASI',9415228637,'SANJAY BARANWAL',0, CURRENT_TIMESTAMP,0, CURRENT_TIMESTAMP);</v>
       </c>
       <c r="G79" s="15"/>
-      <c r="I79" s="6" t="s">
+      <c r="H79" s="6" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="80" spans="1:9" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A80"/>
       <c r="B80"/>
       <c r="C80"/>
       <c r="D80"/>
       <c r="E80"/>
       <c r="F80"/>
-      <c r="G80" s="16"/>
+      <c r="G80" s="15"/>
     </row>
     <row r="81" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A81"/>
@@ -4152,7 +4227,7 @@
       <c r="D81"/>
       <c r="E81"/>
       <c r="F81"/>
-      <c r="G81" s="16"/>
+      <c r="G81" s="15"/>
     </row>
     <row r="82" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A82"/>
@@ -4161,7 +4236,7 @@
       <c r="D82"/>
       <c r="E82"/>
       <c r="F82"/>
-      <c r="G82" s="16"/>
+      <c r="G82" s="15"/>
     </row>
     <row r="83" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A83"/>
@@ -4170,7 +4245,7 @@
       <c r="D83"/>
       <c r="E83"/>
       <c r="F83"/>
-      <c r="G83" s="16"/>
+      <c r="G83" s="15"/>
     </row>
     <row r="84" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A84"/>
@@ -4179,7 +4254,7 @@
       <c r="D84"/>
       <c r="E84"/>
       <c r="F84"/>
-      <c r="G84" s="16"/>
+      <c r="G84" s="15"/>
     </row>
     <row r="85" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A85"/>
@@ -4188,7 +4263,7 @@
       <c r="D85"/>
       <c r="E85"/>
       <c r="F85"/>
-      <c r="G85" s="16"/>
+      <c r="G85" s="15"/>
     </row>
     <row r="86" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A86"/>
@@ -4197,7 +4272,7 @@
       <c r="D86"/>
       <c r="E86"/>
       <c r="F86"/>
-      <c r="G86" s="16"/>
+      <c r="G86" s="15"/>
     </row>
     <row r="87" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A87"/>
@@ -4206,7 +4281,7 @@
       <c r="D87"/>
       <c r="E87"/>
       <c r="F87"/>
-      <c r="G87" s="16"/>
+      <c r="G87" s="15"/>
     </row>
     <row r="88" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A88"/>
@@ -4215,7 +4290,7 @@
       <c r="D88"/>
       <c r="E88"/>
       <c r="F88"/>
-      <c r="G88" s="16"/>
+      <c r="G88" s="15"/>
     </row>
     <row r="89" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A89"/>
@@ -4224,7 +4299,7 @@
       <c r="D89"/>
       <c r="E89"/>
       <c r="F89"/>
-      <c r="G89" s="16"/>
+      <c r="G89" s="15"/>
     </row>
     <row r="90" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A90"/>
@@ -4233,7 +4308,7 @@
       <c r="D90"/>
       <c r="E90"/>
       <c r="F90"/>
-      <c r="G90" s="16"/>
+      <c r="G90" s="15"/>
     </row>
     <row r="91" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A91"/>
@@ -4242,7 +4317,7 @@
       <c r="D91"/>
       <c r="E91"/>
       <c r="F91"/>
-      <c r="G91" s="16"/>
+      <c r="G91" s="15"/>
     </row>
     <row r="92" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A92"/>
@@ -4251,7 +4326,7 @@
       <c r="D92"/>
       <c r="E92"/>
       <c r="F92"/>
-      <c r="G92" s="16"/>
+      <c r="G92" s="15"/>
     </row>
     <row r="93" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A93"/>
@@ -4260,7 +4335,7 @@
       <c r="D93"/>
       <c r="E93"/>
       <c r="F93"/>
-      <c r="G93" s="16"/>
+      <c r="G93" s="15"/>
     </row>
     <row r="94" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A94"/>
@@ -4269,7 +4344,7 @@
       <c r="D94"/>
       <c r="E94"/>
       <c r="F94"/>
-      <c r="G94" s="16"/>
+      <c r="G94" s="15"/>
     </row>
     <row r="95" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A95"/>
@@ -4278,7 +4353,7 @@
       <c r="D95"/>
       <c r="E95"/>
       <c r="F95"/>
-      <c r="G95" s="16"/>
+      <c r="G95" s="15"/>
     </row>
     <row r="96" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A96"/>
@@ -4287,7 +4362,7 @@
       <c r="D96"/>
       <c r="E96"/>
       <c r="F96"/>
-      <c r="G96" s="16"/>
+      <c r="G96" s="15"/>
     </row>
     <row r="97" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97"/>
@@ -4296,7 +4371,7 @@
       <c r="D97"/>
       <c r="E97"/>
       <c r="F97"/>
-      <c r="G97" s="16"/>
+      <c r="G97" s="15"/>
     </row>
     <row r="98" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A98"/>
@@ -4305,7 +4380,7 @@
       <c r="D98"/>
       <c r="E98"/>
       <c r="F98"/>
-      <c r="G98" s="16"/>
+      <c r="G98" s="15"/>
     </row>
     <row r="99" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A99"/>
@@ -4314,7 +4389,7 @@
       <c r="D99"/>
       <c r="E99"/>
       <c r="F99"/>
-      <c r="G99" s="16"/>
+      <c r="G99" s="15"/>
     </row>
     <row r="100" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A100"/>
@@ -4323,7 +4398,7 @@
       <c r="D100"/>
       <c r="E100"/>
       <c r="F100"/>
-      <c r="G100" s="16"/>
+      <c r="G100" s="15"/>
     </row>
     <row r="101" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A101"/>
@@ -4332,7 +4407,7 @@
       <c r="D101"/>
       <c r="E101"/>
       <c r="F101"/>
-      <c r="G101" s="16"/>
+      <c r="G101" s="15"/>
     </row>
     <row r="102" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A102"/>
@@ -4341,7 +4416,7 @@
       <c r="D102"/>
       <c r="E102"/>
       <c r="F102"/>
-      <c r="G102" s="16"/>
+      <c r="G102" s="15"/>
     </row>
     <row r="103" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A103"/>
@@ -4350,7 +4425,7 @@
       <c r="D103"/>
       <c r="E103"/>
       <c r="F103"/>
-      <c r="G103" s="16"/>
+      <c r="G103" s="15"/>
     </row>
     <row r="104" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A104"/>
@@ -4359,7 +4434,7 @@
       <c r="D104"/>
       <c r="E104"/>
       <c r="F104"/>
-      <c r="G104" s="16"/>
+      <c r="G104" s="15"/>
     </row>
     <row r="105" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A105"/>
@@ -4368,7 +4443,7 @@
       <c r="D105"/>
       <c r="E105"/>
       <c r="F105"/>
-      <c r="G105" s="16"/>
+      <c r="G105" s="15"/>
     </row>
     <row r="106" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A106"/>
@@ -4377,7 +4452,7 @@
       <c r="D106"/>
       <c r="E106"/>
       <c r="F106"/>
-      <c r="G106" s="16"/>
+      <c r="G106" s="15"/>
     </row>
     <row r="107" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A107"/>
@@ -4386,7 +4461,7 @@
       <c r="D107"/>
       <c r="E107"/>
       <c r="F107"/>
-      <c r="G107" s="16"/>
+      <c r="G107" s="15"/>
     </row>
     <row r="108" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A108"/>
@@ -4395,7 +4470,7 @@
       <c r="D108"/>
       <c r="E108"/>
       <c r="F108"/>
-      <c r="G108" s="16"/>
+      <c r="G108" s="15"/>
     </row>
     <row r="109" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A109"/>
@@ -4404,7 +4479,7 @@
       <c r="D109"/>
       <c r="E109"/>
       <c r="F109"/>
-      <c r="G109" s="16"/>
+      <c r="G109" s="15"/>
     </row>
     <row r="110" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A110"/>
@@ -4413,7 +4488,7 @@
       <c r="D110"/>
       <c r="E110"/>
       <c r="F110"/>
-      <c r="G110" s="16"/>
+      <c r="G110" s="15"/>
     </row>
     <row r="111" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A111"/>
@@ -4422,7 +4497,7 @@
       <c r="D111"/>
       <c r="E111"/>
       <c r="F111"/>
-      <c r="G111" s="16"/>
+      <c r="G111" s="15"/>
     </row>
     <row r="112" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A112"/>
@@ -4431,7 +4506,7 @@
       <c r="D112"/>
       <c r="E112"/>
       <c r="F112"/>
-      <c r="G112" s="16"/>
+      <c r="G112" s="15"/>
     </row>
     <row r="113" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A113"/>
@@ -4440,7 +4515,7 @@
       <c r="D113"/>
       <c r="E113"/>
       <c r="F113"/>
-      <c r="G113" s="16"/>
+      <c r="G113" s="15"/>
     </row>
     <row r="114" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A114"/>
@@ -4449,7 +4524,7 @@
       <c r="D114"/>
       <c r="E114"/>
       <c r="F114"/>
-      <c r="G114" s="16"/>
+      <c r="G114" s="15"/>
     </row>
     <row r="115" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A115"/>
@@ -4458,7 +4533,7 @@
       <c r="D115"/>
       <c r="E115"/>
       <c r="F115"/>
-      <c r="G115" s="16"/>
+      <c r="G115" s="15"/>
     </row>
     <row r="116" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A116"/>
@@ -4467,7 +4542,7 @@
       <c r="D116"/>
       <c r="E116"/>
       <c r="F116"/>
-      <c r="G116" s="16"/>
+      <c r="G116" s="15"/>
     </row>
     <row r="117" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A117"/>
@@ -4476,7 +4551,7 @@
       <c r="D117"/>
       <c r="E117"/>
       <c r="F117"/>
-      <c r="G117" s="16"/>
+      <c r="G117" s="15"/>
     </row>
     <row r="118" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A118"/>
@@ -4485,7 +4560,7 @@
       <c r="D118"/>
       <c r="E118"/>
       <c r="F118"/>
-      <c r="G118" s="16"/>
+      <c r="G118" s="15"/>
     </row>
     <row r="119" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A119"/>
@@ -4494,7 +4569,7 @@
       <c r="D119"/>
       <c r="E119"/>
       <c r="F119"/>
-      <c r="G119" s="16"/>
+      <c r="G119" s="15"/>
     </row>
     <row r="120" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A120"/>
@@ -4503,7 +4578,7 @@
       <c r="D120"/>
       <c r="E120"/>
       <c r="F120"/>
-      <c r="G120" s="16"/>
+      <c r="G120" s="15"/>
     </row>
     <row r="121" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A121"/>
@@ -4512,7 +4587,7 @@
       <c r="D121"/>
       <c r="E121"/>
       <c r="F121"/>
-      <c r="G121" s="16"/>
+      <c r="G121" s="15"/>
     </row>
     <row r="122" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A122"/>
@@ -4521,7 +4596,7 @@
       <c r="D122"/>
       <c r="E122"/>
       <c r="F122"/>
-      <c r="G122" s="16"/>
+      <c r="G122" s="15"/>
     </row>
     <row r="123" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A123"/>
@@ -4530,7 +4605,7 @@
       <c r="D123"/>
       <c r="E123"/>
       <c r="F123"/>
-      <c r="G123" s="16"/>
+      <c r="G123" s="15"/>
     </row>
     <row r="124" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A124"/>
@@ -4539,7 +4614,7 @@
       <c r="D124"/>
       <c r="E124"/>
       <c r="F124"/>
-      <c r="G124" s="16"/>
+      <c r="G124" s="15"/>
     </row>
     <row r="125" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A125"/>
@@ -4548,7 +4623,7 @@
       <c r="D125"/>
       <c r="E125"/>
       <c r="F125"/>
-      <c r="G125" s="16"/>
+      <c r="G125" s="15"/>
     </row>
     <row r="126" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A126"/>
@@ -4557,7 +4632,7 @@
       <c r="D126"/>
       <c r="E126"/>
       <c r="F126"/>
-      <c r="G126" s="16"/>
+      <c r="G126" s="15"/>
     </row>
     <row r="127" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A127"/>
@@ -4566,7 +4641,7 @@
       <c r="D127"/>
       <c r="E127"/>
       <c r="F127"/>
-      <c r="G127" s="16"/>
+      <c r="G127" s="15"/>
     </row>
     <row r="128" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A128"/>
@@ -4575,7 +4650,7 @@
       <c r="D128"/>
       <c r="E128"/>
       <c r="F128"/>
-      <c r="G128" s="16"/>
+      <c r="G128" s="15"/>
     </row>
     <row r="129" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A129"/>
@@ -4584,7 +4659,7 @@
       <c r="D129"/>
       <c r="E129"/>
       <c r="F129"/>
-      <c r="G129" s="16"/>
+      <c r="G129" s="15"/>
     </row>
     <row r="130" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A130"/>
@@ -4593,7 +4668,7 @@
       <c r="D130"/>
       <c r="E130"/>
       <c r="F130"/>
-      <c r="G130" s="16"/>
+      <c r="G130" s="15"/>
     </row>
     <row r="131" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A131"/>
@@ -4602,7 +4677,7 @@
       <c r="D131"/>
       <c r="E131"/>
       <c r="F131"/>
-      <c r="G131" s="16"/>
+      <c r="G131" s="15"/>
     </row>
     <row r="132" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A132"/>
@@ -4611,7 +4686,7 @@
       <c r="D132"/>
       <c r="E132"/>
       <c r="F132"/>
-      <c r="G132" s="16"/>
+      <c r="G132" s="15"/>
     </row>
     <row r="133" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A133"/>
@@ -4620,7 +4695,7 @@
       <c r="D133"/>
       <c r="E133"/>
       <c r="F133"/>
-      <c r="G133" s="16"/>
+      <c r="G133" s="15"/>
     </row>
     <row r="134" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A134"/>
@@ -4629,7 +4704,7 @@
       <c r="D134"/>
       <c r="E134"/>
       <c r="F134"/>
-      <c r="G134" s="16"/>
+      <c r="G134" s="15"/>
     </row>
     <row r="135" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A135"/>
@@ -4638,7 +4713,7 @@
       <c r="D135"/>
       <c r="E135"/>
       <c r="F135"/>
-      <c r="G135" s="16"/>
+      <c r="G135" s="15"/>
     </row>
     <row r="136" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A136"/>
@@ -4647,7 +4722,7 @@
       <c r="D136"/>
       <c r="E136"/>
       <c r="F136"/>
-      <c r="G136" s="16"/>
+      <c r="G136" s="15"/>
     </row>
     <row r="137" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A137"/>
@@ -4656,7 +4731,7 @@
       <c r="D137"/>
       <c r="E137"/>
       <c r="F137"/>
-      <c r="G137" s="16"/>
+      <c r="G137" s="15"/>
     </row>
     <row r="138" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A138"/>
@@ -4665,7 +4740,7 @@
       <c r="D138"/>
       <c r="E138"/>
       <c r="F138"/>
-      <c r="G138" s="16"/>
+      <c r="G138" s="15"/>
     </row>
     <row r="139" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A139"/>
@@ -4674,7 +4749,7 @@
       <c r="D139"/>
       <c r="E139"/>
       <c r="F139"/>
-      <c r="G139" s="16"/>
+      <c r="G139" s="15"/>
     </row>
     <row r="140" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A140"/>
@@ -4683,7 +4758,7 @@
       <c r="D140"/>
       <c r="E140"/>
       <c r="F140"/>
-      <c r="G140" s="16"/>
+      <c r="G140" s="15"/>
     </row>
     <row r="141" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A141"/>
@@ -4692,7 +4767,7 @@
       <c r="D141"/>
       <c r="E141"/>
       <c r="F141"/>
-      <c r="G141" s="16"/>
+      <c r="G141" s="15"/>
     </row>
     <row r="142" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A142"/>
@@ -4701,7 +4776,7 @@
       <c r="D142"/>
       <c r="E142"/>
       <c r="F142"/>
-      <c r="G142" s="16"/>
+      <c r="G142" s="15"/>
     </row>
     <row r="143" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A143"/>
@@ -4710,7 +4785,7 @@
       <c r="D143"/>
       <c r="E143"/>
       <c r="F143"/>
-      <c r="G143" s="16"/>
+      <c r="G143" s="15"/>
     </row>
     <row r="144" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A144"/>
@@ -4719,7 +4794,7 @@
       <c r="D144"/>
       <c r="E144"/>
       <c r="F144"/>
-      <c r="G144" s="16"/>
+      <c r="G144" s="15"/>
     </row>
     <row r="145" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A145"/>
@@ -4728,7 +4803,7 @@
       <c r="D145"/>
       <c r="E145"/>
       <c r="F145"/>
-      <c r="G145" s="16"/>
+      <c r="G145" s="15"/>
     </row>
     <row r="146" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A146"/>
@@ -4737,7 +4812,7 @@
       <c r="D146"/>
       <c r="E146"/>
       <c r="F146"/>
-      <c r="G146" s="16"/>
+      <c r="G146" s="15"/>
     </row>
     <row r="147" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A147"/>
@@ -4746,7 +4821,7 @@
       <c r="D147"/>
       <c r="E147"/>
       <c r="F147"/>
-      <c r="G147" s="16"/>
+      <c r="G147" s="15"/>
     </row>
     <row r="148" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A148"/>
@@ -4755,7 +4830,7 @@
       <c r="D148"/>
       <c r="E148"/>
       <c r="F148"/>
-      <c r="G148" s="16"/>
+      <c r="G148" s="15"/>
     </row>
     <row r="149" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A149"/>
@@ -4764,7 +4839,7 @@
       <c r="D149"/>
       <c r="E149"/>
       <c r="F149"/>
-      <c r="G149" s="16"/>
+      <c r="G149" s="15"/>
     </row>
     <row r="150" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A150"/>
@@ -4773,7 +4848,7 @@
       <c r="D150"/>
       <c r="E150"/>
       <c r="F150"/>
-      <c r="G150" s="16"/>
+      <c r="G150" s="15"/>
     </row>
     <row r="151" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A151"/>
@@ -4782,7 +4857,7 @@
       <c r="D151"/>
       <c r="E151"/>
       <c r="F151"/>
-      <c r="G151" s="16"/>
+      <c r="G151" s="15"/>
     </row>
     <row r="152" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A152"/>
@@ -4791,7 +4866,7 @@
       <c r="D152"/>
       <c r="E152"/>
       <c r="F152"/>
-      <c r="G152" s="16"/>
+      <c r="G152" s="15"/>
     </row>
     <row r="153" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A153"/>
@@ -4800,7 +4875,7 @@
       <c r="D153"/>
       <c r="E153"/>
       <c r="F153"/>
-      <c r="G153" s="16"/>
+      <c r="G153" s="15"/>
     </row>
     <row r="154" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A154"/>
@@ -4809,7 +4884,7 @@
       <c r="D154"/>
       <c r="E154"/>
       <c r="F154"/>
-      <c r="G154" s="16"/>
+      <c r="G154" s="15"/>
     </row>
     <row r="155" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A155"/>
@@ -4818,7 +4893,7 @@
       <c r="D155"/>
       <c r="E155"/>
       <c r="F155"/>
-      <c r="G155" s="16"/>
+      <c r="G155" s="15"/>
     </row>
     <row r="156" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A156"/>
@@ -4827,7 +4902,7 @@
       <c r="D156"/>
       <c r="E156"/>
       <c r="F156"/>
-      <c r="G156" s="16"/>
+      <c r="G156" s="15"/>
     </row>
     <row r="157" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A157"/>
@@ -4836,7 +4911,7 @@
       <c r="D157"/>
       <c r="E157"/>
       <c r="F157"/>
-      <c r="G157" s="16"/>
+      <c r="G157" s="15"/>
     </row>
     <row r="158" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A158"/>
@@ -4845,7 +4920,7 @@
       <c r="D158"/>
       <c r="E158"/>
       <c r="F158"/>
-      <c r="G158" s="16"/>
+      <c r="G158" s="15"/>
     </row>
     <row r="159" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A159"/>
@@ -4854,7 +4929,7 @@
       <c r="D159"/>
       <c r="E159"/>
       <c r="F159"/>
-      <c r="G159" s="16"/>
+      <c r="G159" s="15"/>
     </row>
     <row r="160" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A160"/>
@@ -4863,7 +4938,7 @@
       <c r="D160"/>
       <c r="E160"/>
       <c r="F160"/>
-      <c r="G160" s="16"/>
+      <c r="G160" s="15"/>
     </row>
     <row r="161" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A161"/>
@@ -4872,7 +4947,7 @@
       <c r="D161"/>
       <c r="E161"/>
       <c r="F161"/>
-      <c r="G161" s="16"/>
+      <c r="G161" s="15"/>
     </row>
     <row r="162" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A162"/>
@@ -4881,7 +4956,7 @@
       <c r="D162"/>
       <c r="E162"/>
       <c r="F162"/>
-      <c r="G162" s="16"/>
+      <c r="G162" s="15"/>
     </row>
     <row r="163" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A163"/>
@@ -4890,7 +4965,7 @@
       <c r="D163"/>
       <c r="E163"/>
       <c r="F163"/>
-      <c r="G163" s="16"/>
+      <c r="G163" s="15"/>
     </row>
     <row r="164" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A164"/>
@@ -4899,7 +4974,7 @@
       <c r="D164"/>
       <c r="E164"/>
       <c r="F164"/>
-      <c r="G164" s="16"/>
+      <c r="G164" s="15"/>
     </row>
     <row r="165" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A165"/>
@@ -4908,7 +4983,7 @@
       <c r="D165"/>
       <c r="E165"/>
       <c r="F165"/>
-      <c r="G165" s="16"/>
+      <c r="G165" s="15"/>
     </row>
     <row r="166" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A166"/>
@@ -4917,7 +4992,7 @@
       <c r="D166"/>
       <c r="E166"/>
       <c r="F166"/>
-      <c r="G166" s="16"/>
+      <c r="G166" s="15"/>
     </row>
     <row r="167" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A167"/>
@@ -4926,7 +5001,7 @@
       <c r="D167"/>
       <c r="E167"/>
       <c r="F167"/>
-      <c r="G167" s="16"/>
+      <c r="G167" s="15"/>
     </row>
     <row r="168" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A168"/>
@@ -4935,7 +5010,7 @@
       <c r="D168"/>
       <c r="E168"/>
       <c r="F168"/>
-      <c r="G168" s="16"/>
+      <c r="G168" s="15"/>
     </row>
     <row r="169" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A169"/>
@@ -4944,7 +5019,7 @@
       <c r="D169"/>
       <c r="E169"/>
       <c r="F169"/>
-      <c r="G169" s="16"/>
+      <c r="G169" s="15"/>
     </row>
     <row r="170" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A170"/>
@@ -4953,7 +5028,7 @@
       <c r="D170"/>
       <c r="E170"/>
       <c r="F170"/>
-      <c r="G170" s="16"/>
+      <c r="G170" s="15"/>
     </row>
     <row r="171" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A171"/>
@@ -4962,7 +5037,7 @@
       <c r="D171"/>
       <c r="E171"/>
       <c r="F171"/>
-      <c r="G171" s="16"/>
+      <c r="G171" s="15"/>
     </row>
     <row r="172" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A172"/>
@@ -4971,7 +5046,7 @@
       <c r="D172"/>
       <c r="E172"/>
       <c r="F172"/>
-      <c r="G172" s="16"/>
+      <c r="G172" s="15"/>
     </row>
     <row r="173" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A173"/>
@@ -4980,7 +5055,7 @@
       <c r="D173"/>
       <c r="E173"/>
       <c r="F173"/>
-      <c r="G173" s="16"/>
+      <c r="G173" s="15"/>
     </row>
     <row r="174" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A174"/>
@@ -4989,7 +5064,7 @@
       <c r="D174"/>
       <c r="E174"/>
       <c r="F174"/>
-      <c r="G174" s="16"/>
+      <c r="G174" s="15"/>
     </row>
     <row r="175" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A175"/>
@@ -4998,7 +5073,7 @@
       <c r="D175"/>
       <c r="E175"/>
       <c r="F175"/>
-      <c r="G175" s="16"/>
+      <c r="G175" s="15"/>
     </row>
     <row r="176" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A176"/>
@@ -5007,7 +5082,7 @@
       <c r="D176"/>
       <c r="E176"/>
       <c r="F176"/>
-      <c r="G176" s="16"/>
+      <c r="G176" s="15"/>
     </row>
     <row r="177" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A177"/>
@@ -5016,7 +5091,7 @@
       <c r="D177"/>
       <c r="E177"/>
       <c r="F177"/>
-      <c r="G177" s="16"/>
+      <c r="G177" s="15"/>
     </row>
     <row r="178" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A178"/>
@@ -5025,7 +5100,7 @@
       <c r="D178"/>
       <c r="E178"/>
       <c r="F178"/>
-      <c r="G178" s="16"/>
+      <c r="G178" s="15"/>
     </row>
     <row r="179" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A179"/>
@@ -5034,7 +5109,7 @@
       <c r="D179"/>
       <c r="E179"/>
       <c r="F179"/>
-      <c r="G179" s="16"/>
+      <c r="G179" s="15"/>
     </row>
     <row r="180" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A180"/>
@@ -5043,7 +5118,7 @@
       <c r="D180"/>
       <c r="E180"/>
       <c r="F180"/>
-      <c r="G180" s="16"/>
+      <c r="G180" s="15"/>
     </row>
     <row r="181" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A181"/>
@@ -5052,7 +5127,7 @@
       <c r="D181"/>
       <c r="E181"/>
       <c r="F181"/>
-      <c r="G181" s="16"/>
+      <c r="G181" s="15"/>
     </row>
     <row r="182" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A182"/>
@@ -5061,7 +5136,7 @@
       <c r="D182"/>
       <c r="E182"/>
       <c r="F182"/>
-      <c r="G182" s="16"/>
+      <c r="G182" s="15"/>
     </row>
     <row r="183" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A183"/>
@@ -5070,7 +5145,7 @@
       <c r="D183"/>
       <c r="E183"/>
       <c r="F183"/>
-      <c r="G183" s="16"/>
+      <c r="G183" s="15"/>
     </row>
     <row r="184" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A184"/>
@@ -5079,7 +5154,7 @@
       <c r="D184"/>
       <c r="E184"/>
       <c r="F184"/>
-      <c r="G184" s="16"/>
+      <c r="G184" s="15"/>
     </row>
     <row r="185" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A185"/>
@@ -5088,7 +5163,7 @@
       <c r="D185"/>
       <c r="E185"/>
       <c r="F185"/>
-      <c r="G185" s="16"/>
+      <c r="G185" s="15"/>
     </row>
     <row r="186" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A186"/>
@@ -5097,7 +5172,7 @@
       <c r="D186"/>
       <c r="E186"/>
       <c r="F186"/>
-      <c r="G186" s="16"/>
+      <c r="G186" s="15"/>
     </row>
     <row r="187" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A187"/>
@@ -5106,7 +5181,7 @@
       <c r="D187"/>
       <c r="E187"/>
       <c r="F187"/>
-      <c r="G187" s="16"/>
+      <c r="G187" s="15"/>
     </row>
     <row r="188" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A188"/>
@@ -5115,7 +5190,7 @@
       <c r="D188"/>
       <c r="E188"/>
       <c r="F188"/>
-      <c r="G188" s="16"/>
+      <c r="G188" s="15"/>
     </row>
     <row r="189" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A189"/>
@@ -5124,7 +5199,7 @@
       <c r="D189"/>
       <c r="E189"/>
       <c r="F189"/>
-      <c r="G189" s="16"/>
+      <c r="G189" s="15"/>
     </row>
     <row r="190" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A190"/>
@@ -5133,7 +5208,7 @@
       <c r="D190"/>
       <c r="E190"/>
       <c r="F190"/>
-      <c r="G190" s="16"/>
+      <c r="G190" s="15"/>
     </row>
     <row r="191" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A191"/>
@@ -5142,7 +5217,7 @@
       <c r="D191"/>
       <c r="E191"/>
       <c r="F191"/>
-      <c r="G191" s="16"/>
+      <c r="G191" s="15"/>
     </row>
     <row r="192" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A192"/>
@@ -5151,7 +5226,7 @@
       <c r="D192"/>
       <c r="E192"/>
       <c r="F192"/>
-      <c r="G192" s="16"/>
+      <c r="G192" s="15"/>
     </row>
     <row r="193" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A193"/>
@@ -5160,7 +5235,7 @@
       <c r="D193"/>
       <c r="E193"/>
       <c r="F193"/>
-      <c r="G193" s="16"/>
+      <c r="G193" s="15"/>
     </row>
     <row r="194" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A194"/>
@@ -5169,7 +5244,7 @@
       <c r="D194"/>
       <c r="E194"/>
       <c r="F194"/>
-      <c r="G194" s="16"/>
+      <c r="G194" s="15"/>
     </row>
     <row r="195" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A195"/>
@@ -5178,7 +5253,7 @@
       <c r="D195"/>
       <c r="E195"/>
       <c r="F195"/>
-      <c r="G195" s="16"/>
+      <c r="G195" s="15"/>
     </row>
     <row r="196" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A196"/>
@@ -5187,7 +5262,7 @@
       <c r="D196"/>
       <c r="E196"/>
       <c r="F196"/>
-      <c r="G196" s="16"/>
+      <c r="G196" s="15"/>
     </row>
     <row r="197" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A197"/>
@@ -5196,7 +5271,7 @@
       <c r="D197"/>
       <c r="E197"/>
       <c r="F197"/>
-      <c r="G197" s="16"/>
+      <c r="G197" s="15"/>
     </row>
     <row r="198" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A198"/>
@@ -5205,7 +5280,7 @@
       <c r="D198"/>
       <c r="E198"/>
       <c r="F198"/>
-      <c r="G198" s="16"/>
+      <c r="G198" s="15"/>
     </row>
     <row r="199" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A199"/>
@@ -5214,7 +5289,7 @@
       <c r="D199"/>
       <c r="E199"/>
       <c r="F199"/>
-      <c r="G199" s="16"/>
+      <c r="G199" s="15"/>
     </row>
     <row r="200" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A200"/>
@@ -5223,7 +5298,7 @@
       <c r="D200"/>
       <c r="E200"/>
       <c r="F200"/>
-      <c r="G200" s="16"/>
+      <c r="G200" s="15"/>
     </row>
     <row r="201" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A201"/>
@@ -5232,7 +5307,7 @@
       <c r="D201"/>
       <c r="E201"/>
       <c r="F201"/>
-      <c r="G201" s="16"/>
+      <c r="G201" s="15"/>
     </row>
     <row r="202" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A202"/>
@@ -5241,7 +5316,7 @@
       <c r="D202"/>
       <c r="E202"/>
       <c r="F202"/>
-      <c r="G202" s="16"/>
+      <c r="G202" s="15"/>
     </row>
     <row r="203" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A203"/>
@@ -5250,7 +5325,7 @@
       <c r="D203"/>
       <c r="E203"/>
       <c r="F203"/>
-      <c r="G203" s="16"/>
+      <c r="G203" s="15"/>
     </row>
     <row r="204" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A204"/>
@@ -5259,7 +5334,7 @@
       <c r="D204"/>
       <c r="E204"/>
       <c r="F204"/>
-      <c r="G204" s="16"/>
+      <c r="G204" s="15"/>
     </row>
     <row r="205" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A205"/>
@@ -5268,7 +5343,7 @@
       <c r="D205"/>
       <c r="E205"/>
       <c r="F205"/>
-      <c r="G205" s="16"/>
+      <c r="G205" s="15"/>
     </row>
     <row r="206" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A206"/>
@@ -5277,7 +5352,7 @@
       <c r="D206"/>
       <c r="E206"/>
       <c r="F206"/>
-      <c r="G206" s="16"/>
+      <c r="G206" s="15"/>
     </row>
     <row r="207" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A207"/>
@@ -5286,7 +5361,7 @@
       <c r="D207"/>
       <c r="E207"/>
       <c r="F207"/>
-      <c r="G207" s="16"/>
+      <c r="G207" s="15"/>
     </row>
     <row r="208" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A208"/>
@@ -5295,7 +5370,7 @@
       <c r="D208"/>
       <c r="E208"/>
       <c r="F208"/>
-      <c r="G208" s="16"/>
+      <c r="G208" s="15"/>
     </row>
     <row r="209" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A209"/>
@@ -5304,7 +5379,7 @@
       <c r="D209"/>
       <c r="E209"/>
       <c r="F209"/>
-      <c r="G209" s="16"/>
+      <c r="G209" s="15"/>
     </row>
     <row r="210" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A210"/>
@@ -5313,7 +5388,7 @@
       <c r="D210"/>
       <c r="E210"/>
       <c r="F210"/>
-      <c r="G210" s="16"/>
+      <c r="G210" s="15"/>
     </row>
     <row r="211" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A211"/>
@@ -5322,7 +5397,7 @@
       <c r="D211"/>
       <c r="E211"/>
       <c r="F211"/>
-      <c r="G211" s="16"/>
+      <c r="G211" s="15"/>
     </row>
     <row r="212" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A212"/>
@@ -5331,7 +5406,7 @@
       <c r="D212"/>
       <c r="E212"/>
       <c r="F212"/>
-      <c r="G212" s="16"/>
+      <c r="G212" s="15"/>
     </row>
     <row r="213" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A213"/>
@@ -5340,7 +5415,7 @@
       <c r="D213"/>
       <c r="E213"/>
       <c r="F213"/>
-      <c r="G213" s="16"/>
+      <c r="G213" s="15"/>
     </row>
     <row r="214" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A214"/>
@@ -5349,7 +5424,7 @@
       <c r="D214"/>
       <c r="E214"/>
       <c r="F214"/>
-      <c r="G214" s="16"/>
+      <c r="G214" s="15"/>
     </row>
     <row r="215" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A215"/>
@@ -5358,7 +5433,7 @@
       <c r="D215"/>
       <c r="E215"/>
       <c r="F215"/>
-      <c r="G215" s="16"/>
+      <c r="G215" s="15"/>
     </row>
     <row r="216" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A216"/>
@@ -5367,7 +5442,7 @@
       <c r="D216"/>
       <c r="E216"/>
       <c r="F216"/>
-      <c r="G216" s="16"/>
+      <c r="G216" s="15"/>
     </row>
     <row r="217" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A217"/>
@@ -5376,7 +5451,7 @@
       <c r="D217"/>
       <c r="E217"/>
       <c r="F217"/>
-      <c r="G217" s="16"/>
+      <c r="G217" s="15"/>
     </row>
     <row r="218" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A218"/>
@@ -5385,7 +5460,7 @@
       <c r="D218"/>
       <c r="E218"/>
       <c r="F218"/>
-      <c r="G218" s="16"/>
+      <c r="G218" s="15"/>
     </row>
     <row r="219" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A219"/>
@@ -5394,7 +5469,7 @@
       <c r="D219"/>
       <c r="E219"/>
       <c r="F219"/>
-      <c r="G219" s="16"/>
+      <c r="G219" s="15"/>
     </row>
     <row r="220" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A220"/>
@@ -5403,7 +5478,7 @@
       <c r="D220"/>
       <c r="E220"/>
       <c r="F220"/>
-      <c r="G220" s="16"/>
+      <c r="G220" s="15"/>
     </row>
     <row r="221" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A221"/>
@@ -5412,7 +5487,7 @@
       <c r="D221"/>
       <c r="E221"/>
       <c r="F221"/>
-      <c r="G221" s="16"/>
+      <c r="G221" s="15"/>
     </row>
     <row r="222" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A222"/>
@@ -5421,7 +5496,7 @@
       <c r="D222"/>
       <c r="E222"/>
       <c r="F222"/>
-      <c r="G222" s="16"/>
+      <c r="G222" s="15"/>
     </row>
     <row r="223" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A223"/>
@@ -5430,7 +5505,7 @@
       <c r="D223"/>
       <c r="E223"/>
       <c r="F223"/>
-      <c r="G223" s="16"/>
+      <c r="G223" s="15"/>
     </row>
     <row r="224" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A224"/>
@@ -5439,7 +5514,7 @@
       <c r="D224"/>
       <c r="E224"/>
       <c r="F224"/>
-      <c r="G224" s="16"/>
+      <c r="G224" s="15"/>
     </row>
     <row r="225" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A225"/>
@@ -5448,7 +5523,7 @@
       <c r="D225"/>
       <c r="E225"/>
       <c r="F225"/>
-      <c r="G225" s="16"/>
+      <c r="G225" s="15"/>
     </row>
     <row r="226" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A226"/>
@@ -5457,7 +5532,7 @@
       <c r="D226"/>
       <c r="E226"/>
       <c r="F226"/>
-      <c r="G226" s="16"/>
+      <c r="G226" s="15"/>
     </row>
     <row r="227" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A227"/>
@@ -5466,7 +5541,7 @@
       <c r="D227"/>
       <c r="E227"/>
       <c r="F227"/>
-      <c r="G227" s="16"/>
+      <c r="G227" s="15"/>
     </row>
     <row r="228" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A228"/>
@@ -5475,7 +5550,7 @@
       <c r="D228"/>
       <c r="E228"/>
       <c r="F228"/>
-      <c r="G228" s="16"/>
+      <c r="G228" s="15"/>
     </row>
     <row r="229" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A229"/>
@@ -5484,7 +5559,7 @@
       <c r="D229"/>
       <c r="E229"/>
       <c r="F229"/>
-      <c r="G229" s="16"/>
+      <c r="G229" s="15"/>
     </row>
     <row r="230" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A230"/>
@@ -5493,7 +5568,7 @@
       <c r="D230"/>
       <c r="E230"/>
       <c r="F230"/>
-      <c r="G230" s="16"/>
+      <c r="G230" s="15"/>
     </row>
     <row r="231" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A231"/>
@@ -5502,7 +5577,7 @@
       <c r="D231"/>
       <c r="E231"/>
       <c r="F231"/>
-      <c r="G231" s="16"/>
+      <c r="G231" s="15"/>
     </row>
     <row r="232" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A232"/>
@@ -5511,7 +5586,7 @@
       <c r="D232"/>
       <c r="E232"/>
       <c r="F232"/>
-      <c r="G232" s="16"/>
+      <c r="G232" s="15"/>
     </row>
     <row r="233" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A233"/>
@@ -5520,7 +5595,7 @@
       <c r="D233"/>
       <c r="E233"/>
       <c r="F233"/>
-      <c r="G233" s="16"/>
+      <c r="G233" s="15"/>
     </row>
     <row r="234" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A234"/>
@@ -5529,7 +5604,7 @@
       <c r="D234"/>
       <c r="E234"/>
       <c r="F234"/>
-      <c r="G234" s="16"/>
+      <c r="G234" s="15"/>
     </row>
     <row r="235" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A235"/>
@@ -5538,7 +5613,7 @@
       <c r="D235"/>
       <c r="E235"/>
       <c r="F235"/>
-      <c r="G235" s="16"/>
+      <c r="G235" s="15"/>
     </row>
     <row r="236" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A236"/>
@@ -5547,7 +5622,7 @@
       <c r="D236"/>
       <c r="E236"/>
       <c r="F236"/>
-      <c r="G236" s="16"/>
+      <c r="G236" s="15"/>
     </row>
     <row r="237" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A237"/>
@@ -5556,7 +5631,7 @@
       <c r="D237"/>
       <c r="E237"/>
       <c r="F237"/>
-      <c r="G237" s="16"/>
+      <c r="G237" s="15"/>
     </row>
     <row r="238" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A238"/>
@@ -5565,7 +5640,7 @@
       <c r="D238"/>
       <c r="E238"/>
       <c r="F238"/>
-      <c r="G238" s="16"/>
+      <c r="G238" s="15"/>
     </row>
     <row r="239" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A239"/>
@@ -5574,7 +5649,7 @@
       <c r="D239"/>
       <c r="E239"/>
       <c r="F239"/>
-      <c r="G239" s="16"/>
+      <c r="G239" s="15"/>
     </row>
     <row r="240" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A240"/>
@@ -5583,7 +5658,7 @@
       <c r="D240"/>
       <c r="E240"/>
       <c r="F240"/>
-      <c r="G240" s="16"/>
+      <c r="G240" s="15"/>
     </row>
     <row r="241" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A241"/>
@@ -5592,7 +5667,7 @@
       <c r="D241"/>
       <c r="E241"/>
       <c r="F241"/>
-      <c r="G241" s="16"/>
+      <c r="G241" s="15"/>
     </row>
     <row r="242" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A242"/>
@@ -5601,7 +5676,7 @@
       <c r="D242"/>
       <c r="E242"/>
       <c r="F242"/>
-      <c r="G242" s="16"/>
+      <c r="G242" s="15"/>
     </row>
     <row r="243" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A243"/>
@@ -5610,7 +5685,7 @@
       <c r="D243"/>
       <c r="E243"/>
       <c r="F243"/>
-      <c r="G243" s="16"/>
+      <c r="G243" s="15"/>
     </row>
     <row r="244" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A244"/>
@@ -5619,7 +5694,7 @@
       <c r="D244"/>
       <c r="E244"/>
       <c r="F244"/>
-      <c r="G244" s="16"/>
+      <c r="G244" s="15"/>
     </row>
     <row r="245" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A245"/>
@@ -5628,7 +5703,7 @@
       <c r="D245"/>
       <c r="E245"/>
       <c r="F245"/>
-      <c r="G245" s="16"/>
+      <c r="G245" s="15"/>
     </row>
     <row r="246" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A246"/>
@@ -5637,7 +5712,7 @@
       <c r="D246"/>
       <c r="E246"/>
       <c r="F246"/>
-      <c r="G246" s="16"/>
+      <c r="G246" s="15"/>
     </row>
     <row r="247" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A247"/>
@@ -5646,7 +5721,7 @@
       <c r="D247"/>
       <c r="E247"/>
       <c r="F247"/>
-      <c r="G247" s="16"/>
+      <c r="G247" s="15"/>
     </row>
     <row r="248" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A248"/>
@@ -5655,7 +5730,7 @@
       <c r="D248"/>
       <c r="E248"/>
       <c r="F248"/>
-      <c r="G248" s="16"/>
+      <c r="G248" s="15"/>
     </row>
     <row r="249" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A249"/>
@@ -5664,7 +5739,7 @@
       <c r="D249"/>
       <c r="E249"/>
       <c r="F249"/>
-      <c r="G249" s="16"/>
+      <c r="G249" s="15"/>
     </row>
     <row r="250" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A250"/>
@@ -5673,7 +5748,7 @@
       <c r="D250"/>
       <c r="E250"/>
       <c r="F250"/>
-      <c r="G250" s="16"/>
+      <c r="G250" s="15"/>
     </row>
     <row r="251" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A251"/>
@@ -5682,7 +5757,7 @@
       <c r="D251"/>
       <c r="E251"/>
       <c r="F251"/>
-      <c r="G251" s="16"/>
+      <c r="G251" s="15"/>
     </row>
     <row r="252" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A252"/>
@@ -5691,7 +5766,7 @@
       <c r="D252"/>
       <c r="E252"/>
       <c r="F252"/>
-      <c r="G252" s="16"/>
+      <c r="G252" s="15"/>
     </row>
     <row r="253" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A253"/>
@@ -5700,7 +5775,7 @@
       <c r="D253"/>
       <c r="E253"/>
       <c r="F253"/>
-      <c r="G253" s="16"/>
+      <c r="G253" s="15"/>
     </row>
     <row r="254" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A254"/>
@@ -5709,7 +5784,7 @@
       <c r="D254"/>
       <c r="E254"/>
       <c r="F254"/>
-      <c r="G254" s="16"/>
+      <c r="G254" s="15"/>
     </row>
     <row r="255" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A255"/>
@@ -5718,7 +5793,7 @@
       <c r="D255"/>
       <c r="E255"/>
       <c r="F255"/>
-      <c r="G255" s="16"/>
+      <c r="G255" s="15"/>
     </row>
     <row r="256" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A256"/>
@@ -5727,7 +5802,7 @@
       <c r="D256"/>
       <c r="E256"/>
       <c r="F256"/>
-      <c r="G256" s="16"/>
+      <c r="G256" s="15"/>
     </row>
     <row r="257" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A257"/>
@@ -5736,7 +5811,7 @@
       <c r="D257"/>
       <c r="E257"/>
       <c r="F257"/>
-      <c r="G257" s="16"/>
+      <c r="G257" s="15"/>
     </row>
     <row r="258" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A258"/>
@@ -5745,7 +5820,7 @@
       <c r="D258"/>
       <c r="E258"/>
       <c r="F258"/>
-      <c r="G258" s="16"/>
+      <c r="G258" s="15"/>
     </row>
     <row r="259" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A259"/>
@@ -5754,7 +5829,7 @@
       <c r="D259"/>
       <c r="E259"/>
       <c r="F259"/>
-      <c r="G259" s="16"/>
+      <c r="G259" s="15"/>
     </row>
     <row r="260" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A260"/>
@@ -5763,7 +5838,7 @@
       <c r="D260"/>
       <c r="E260"/>
       <c r="F260"/>
-      <c r="G260" s="16"/>
+      <c r="G260" s="15"/>
     </row>
     <row r="261" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A261"/>
@@ -5772,7 +5847,7 @@
       <c r="D261"/>
       <c r="E261"/>
       <c r="F261"/>
-      <c r="G261" s="16"/>
+      <c r="G261" s="15"/>
     </row>
     <row r="262" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A262"/>
@@ -5781,7 +5856,7 @@
       <c r="D262"/>
       <c r="E262"/>
       <c r="F262"/>
-      <c r="G262" s="16"/>
+      <c r="G262" s="15"/>
     </row>
     <row r="263" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A263"/>
@@ -5790,7 +5865,7 @@
       <c r="D263"/>
       <c r="E263"/>
       <c r="F263"/>
-      <c r="G263" s="16"/>
+      <c r="G263" s="15"/>
     </row>
     <row r="264" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A264"/>
@@ -5799,7 +5874,7 @@
       <c r="D264"/>
       <c r="E264"/>
       <c r="F264"/>
-      <c r="G264" s="16"/>
+      <c r="G264" s="15"/>
     </row>
     <row r="265" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A265"/>
@@ -5808,7 +5883,7 @@
       <c r="D265"/>
       <c r="E265"/>
       <c r="F265"/>
-      <c r="G265" s="16"/>
+      <c r="G265" s="15"/>
     </row>
     <row r="266" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A266"/>
@@ -5817,7 +5892,7 @@
       <c r="D266"/>
       <c r="E266"/>
       <c r="F266"/>
-      <c r="G266" s="16"/>
+      <c r="G266" s="15"/>
     </row>
     <row r="267" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A267"/>
@@ -5826,7 +5901,7 @@
       <c r="D267"/>
       <c r="E267"/>
       <c r="F267"/>
-      <c r="G267" s="16"/>
+      <c r="G267" s="15"/>
     </row>
     <row r="268" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A268"/>
@@ -5835,7 +5910,7 @@
       <c r="D268"/>
       <c r="E268"/>
       <c r="F268"/>
-      <c r="G268" s="16"/>
+      <c r="G268" s="15"/>
     </row>
     <row r="269" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A269"/>
@@ -5844,7 +5919,7 @@
       <c r="D269"/>
       <c r="E269"/>
       <c r="F269"/>
-      <c r="G269" s="16"/>
+      <c r="G269" s="15"/>
     </row>
     <row r="270" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A270"/>
@@ -5853,7 +5928,7 @@
       <c r="D270"/>
       <c r="E270"/>
       <c r="F270"/>
-      <c r="G270" s="16"/>
+      <c r="G270" s="15"/>
     </row>
     <row r="271" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A271"/>
@@ -5862,7 +5937,7 @@
       <c r="D271"/>
       <c r="E271"/>
       <c r="F271"/>
-      <c r="G271" s="16"/>
+      <c r="G271" s="15"/>
     </row>
     <row r="272" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A272"/>
@@ -5871,7 +5946,7 @@
       <c r="D272"/>
       <c r="E272"/>
       <c r="F272"/>
-      <c r="G272" s="16"/>
+      <c r="G272" s="15"/>
     </row>
     <row r="273" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A273"/>
@@ -5880,7 +5955,7 @@
       <c r="D273"/>
       <c r="E273"/>
       <c r="F273"/>
-      <c r="G273" s="16"/>
+      <c r="G273" s="15"/>
     </row>
     <row r="274" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A274"/>
@@ -5889,7 +5964,7 @@
       <c r="D274"/>
       <c r="E274"/>
       <c r="F274"/>
-      <c r="G274" s="16"/>
+      <c r="G274" s="15"/>
     </row>
     <row r="275" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A275"/>
@@ -5898,7 +5973,7 @@
       <c r="D275"/>
       <c r="E275"/>
       <c r="F275"/>
-      <c r="G275" s="16"/>
+      <c r="G275" s="15"/>
     </row>
     <row r="276" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A276"/>
@@ -5907,7 +5982,7 @@
       <c r="D276"/>
       <c r="E276"/>
       <c r="F276"/>
-      <c r="G276" s="16"/>
+      <c r="G276" s="15"/>
     </row>
     <row r="277" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A277"/>
@@ -5916,7 +5991,7 @@
       <c r="D277"/>
       <c r="E277"/>
       <c r="F277"/>
-      <c r="G277" s="16"/>
+      <c r="G277" s="15"/>
     </row>
     <row r="278" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A278"/>
@@ -5925,7 +6000,7 @@
       <c r="D278"/>
       <c r="E278"/>
       <c r="F278"/>
-      <c r="G278" s="16"/>
+      <c r="G278" s="15"/>
     </row>
     <row r="279" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A279"/>
@@ -5934,7 +6009,7 @@
       <c r="D279"/>
       <c r="E279"/>
       <c r="F279"/>
-      <c r="G279" s="16"/>
+      <c r="G279" s="15"/>
     </row>
     <row r="280" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A280"/>
@@ -5943,7 +6018,7 @@
       <c r="D280"/>
       <c r="E280"/>
       <c r="F280"/>
-      <c r="G280" s="16"/>
+      <c r="G280" s="15"/>
     </row>
     <row r="281" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A281"/>
@@ -5952,7 +6027,7 @@
       <c r="D281"/>
       <c r="E281"/>
       <c r="F281"/>
-      <c r="G281" s="16"/>
+      <c r="G281" s="15"/>
     </row>
     <row r="282" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A282"/>
@@ -5961,7 +6036,7 @@
       <c r="D282"/>
       <c r="E282"/>
       <c r="F282"/>
-      <c r="G282" s="16"/>
+      <c r="G282" s="15"/>
     </row>
     <row r="283" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A283"/>
@@ -5970,7 +6045,7 @@
       <c r="D283"/>
       <c r="E283"/>
       <c r="F283"/>
-      <c r="G283" s="16"/>
+      <c r="G283" s="15"/>
     </row>
     <row r="284" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A284"/>
@@ -5979,7 +6054,7 @@
       <c r="D284"/>
       <c r="E284"/>
       <c r="F284"/>
-      <c r="G284" s="16"/>
+      <c r="G284" s="15"/>
     </row>
     <row r="285" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A285"/>
@@ -5988,7 +6063,7 @@
       <c r="D285"/>
       <c r="E285"/>
       <c r="F285"/>
-      <c r="G285" s="16"/>
+      <c r="G285" s="15"/>
     </row>
     <row r="286" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A286"/>
@@ -5997,7 +6072,7 @@
       <c r="D286"/>
       <c r="E286"/>
       <c r="F286"/>
-      <c r="G286" s="16"/>
+      <c r="G286" s="15"/>
     </row>
     <row r="287" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A287"/>
@@ -6006,7 +6081,7 @@
       <c r="D287"/>
       <c r="E287"/>
       <c r="F287"/>
-      <c r="G287" s="16"/>
+      <c r="G287" s="15"/>
     </row>
     <row r="288" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A288"/>
@@ -6015,7 +6090,7 @@
       <c r="D288"/>
       <c r="E288"/>
       <c r="F288"/>
-      <c r="G288" s="16"/>
+      <c r="G288" s="15"/>
     </row>
     <row r="289" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A289"/>
@@ -6024,7 +6099,7 @@
       <c r="D289"/>
       <c r="E289"/>
       <c r="F289"/>
-      <c r="G289" s="16"/>
+      <c r="G289" s="15"/>
     </row>
     <row r="290" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A290"/>
@@ -6033,7 +6108,7 @@
       <c r="D290"/>
       <c r="E290"/>
       <c r="F290"/>
-      <c r="G290" s="16"/>
+      <c r="G290" s="15"/>
     </row>
     <row r="291" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A291"/>
@@ -6042,7 +6117,7 @@
       <c r="D291"/>
       <c r="E291"/>
       <c r="F291"/>
-      <c r="G291" s="16"/>
+      <c r="G291" s="15"/>
     </row>
     <row r="292" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A292"/>
@@ -6051,7 +6126,7 @@
       <c r="D292"/>
       <c r="E292"/>
       <c r="F292"/>
-      <c r="G292" s="16"/>
+      <c r="G292" s="15"/>
     </row>
     <row r="293" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A293"/>
@@ -6060,7 +6135,7 @@
       <c r="D293"/>
       <c r="E293"/>
       <c r="F293"/>
-      <c r="G293" s="16"/>
+      <c r="G293" s="15"/>
     </row>
     <row r="294" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A294"/>
@@ -6069,7 +6144,7 @@
       <c r="D294"/>
       <c r="E294"/>
       <c r="F294"/>
-      <c r="G294" s="16"/>
+      <c r="G294" s="15"/>
     </row>
     <row r="295" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A295"/>
@@ -6078,7 +6153,7 @@
       <c r="D295"/>
       <c r="E295"/>
       <c r="F295"/>
-      <c r="G295" s="16"/>
+      <c r="G295" s="15"/>
     </row>
     <row r="296" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A296"/>
@@ -6087,7 +6162,7 @@
       <c r="D296"/>
       <c r="E296"/>
       <c r="F296"/>
-      <c r="G296" s="16"/>
+      <c r="G296" s="15"/>
     </row>
     <row r="297" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A297"/>
@@ -6096,7 +6171,7 @@
       <c r="D297"/>
       <c r="E297"/>
       <c r="F297"/>
-      <c r="G297" s="16"/>
+      <c r="G297" s="15"/>
     </row>
     <row r="298" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A298"/>
@@ -6105,7 +6180,7 @@
       <c r="D298"/>
       <c r="E298"/>
       <c r="F298"/>
-      <c r="G298" s="16"/>
+      <c r="G298" s="15"/>
     </row>
     <row r="299" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A299"/>
@@ -6114,7 +6189,7 @@
       <c r="D299"/>
       <c r="E299"/>
       <c r="F299"/>
-      <c r="G299" s="16"/>
+      <c r="G299" s="15"/>
     </row>
     <row r="300" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A300"/>
@@ -6123,7 +6198,7 @@
       <c r="D300"/>
       <c r="E300"/>
       <c r="F300"/>
-      <c r="G300" s="16"/>
+      <c r="G300" s="15"/>
     </row>
     <row r="301" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A301"/>
@@ -6132,7 +6207,7 @@
       <c r="D301"/>
       <c r="E301"/>
       <c r="F301"/>
-      <c r="G301" s="16"/>
+      <c r="G301" s="15"/>
     </row>
     <row r="302" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A302"/>
@@ -6141,7 +6216,7 @@
       <c r="D302"/>
       <c r="E302"/>
       <c r="F302"/>
-      <c r="G302" s="16"/>
+      <c r="G302" s="15"/>
     </row>
     <row r="303" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A303"/>
@@ -6150,7 +6225,7 @@
       <c r="D303"/>
       <c r="E303"/>
       <c r="F303"/>
-      <c r="G303" s="16"/>
+      <c r="G303" s="15"/>
     </row>
     <row r="304" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A304"/>
@@ -6159,7 +6234,7 @@
       <c r="D304"/>
       <c r="E304"/>
       <c r="F304"/>
-      <c r="G304" s="16"/>
+      <c r="G304" s="15"/>
     </row>
     <row r="305" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A305"/>
@@ -6168,7 +6243,7 @@
       <c r="D305"/>
       <c r="E305"/>
       <c r="F305"/>
-      <c r="G305" s="16"/>
+      <c r="G305" s="15"/>
     </row>
     <row r="306" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A306"/>
@@ -6177,7 +6252,7 @@
       <c r="D306"/>
       <c r="E306"/>
       <c r="F306"/>
-      <c r="G306" s="16"/>
+      <c r="G306" s="15"/>
     </row>
     <row r="307" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A307"/>
@@ -6186,7 +6261,7 @@
       <c r="D307"/>
       <c r="E307"/>
       <c r="F307"/>
-      <c r="G307" s="16"/>
+      <c r="G307" s="15"/>
     </row>
     <row r="308" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A308"/>
@@ -6195,7 +6270,7 @@
       <c r="D308"/>
       <c r="E308"/>
       <c r="F308"/>
-      <c r="G308" s="16"/>
+      <c r="G308" s="15"/>
     </row>
     <row r="309" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A309"/>
@@ -6204,7 +6279,7 @@
       <c r="D309"/>
       <c r="E309"/>
       <c r="F309"/>
-      <c r="G309" s="16"/>
+      <c r="G309" s="15"/>
     </row>
     <row r="310" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A310"/>
@@ -6213,7 +6288,7 @@
       <c r="D310"/>
       <c r="E310"/>
       <c r="F310"/>
-      <c r="G310" s="16"/>
+      <c r="G310" s="15"/>
     </row>
     <row r="311" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A311"/>
@@ -6222,7 +6297,7 @@
       <c r="D311"/>
       <c r="E311"/>
       <c r="F311"/>
-      <c r="G311" s="16"/>
+      <c r="G311" s="15"/>
     </row>
     <row r="312" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A312"/>
@@ -6231,7 +6306,7 @@
       <c r="D312"/>
       <c r="E312"/>
       <c r="F312"/>
-      <c r="G312" s="16"/>
+      <c r="G312" s="15"/>
     </row>
     <row r="313" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A313"/>
@@ -6240,7 +6315,7 @@
       <c r="D313"/>
       <c r="E313"/>
       <c r="F313"/>
-      <c r="G313" s="16"/>
+      <c r="G313" s="15"/>
     </row>
     <row r="314" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A314"/>
@@ -6249,7 +6324,7 @@
       <c r="D314"/>
       <c r="E314"/>
       <c r="F314"/>
-      <c r="G314" s="16"/>
+      <c r="G314" s="15"/>
     </row>
     <row r="315" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A315"/>
@@ -6258,7 +6333,7 @@
       <c r="D315"/>
       <c r="E315"/>
       <c r="F315"/>
-      <c r="G315" s="16"/>
+      <c r="G315" s="15"/>
     </row>
     <row r="316" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A316"/>
@@ -6267,7 +6342,7 @@
       <c r="D316"/>
       <c r="E316"/>
       <c r="F316"/>
-      <c r="G316" s="16"/>
+      <c r="G316" s="15"/>
     </row>
     <row r="317" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A317"/>
@@ -6276,7 +6351,7 @@
       <c r="D317"/>
       <c r="E317"/>
       <c r="F317"/>
-      <c r="G317" s="16"/>
+      <c r="G317" s="15"/>
     </row>
     <row r="318" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A318"/>
@@ -6285,7 +6360,7 @@
       <c r="D318"/>
       <c r="E318"/>
       <c r="F318"/>
-      <c r="G318" s="16"/>
+      <c r="G318" s="15"/>
     </row>
     <row r="319" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A319"/>
@@ -6294,7 +6369,7 @@
       <c r="D319"/>
       <c r="E319"/>
       <c r="F319"/>
-      <c r="G319" s="16"/>
+      <c r="G319" s="15"/>
     </row>
     <row r="320" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A320"/>
@@ -6303,7 +6378,7 @@
       <c r="D320"/>
       <c r="E320"/>
       <c r="F320"/>
-      <c r="G320" s="16"/>
+      <c r="G320" s="15"/>
     </row>
     <row r="321" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A321"/>
@@ -6312,7 +6387,7 @@
       <c r="D321"/>
       <c r="E321"/>
       <c r="F321"/>
-      <c r="G321" s="16"/>
+      <c r="G321" s="15"/>
     </row>
     <row r="322" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A322"/>
@@ -6321,7 +6396,7 @@
       <c r="D322"/>
       <c r="E322"/>
       <c r="F322"/>
-      <c r="G322" s="16"/>
+      <c r="G322" s="15"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E322">
@@ -6334,7 +6409,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16CF5799-E893-4846-8838-730C9C00B355}">
-  <dimension ref="A1:G322"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -6344,9 +6419,10 @@
     <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.1640625" customWidth="1"/>
     <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6369,7 +6445,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>9110032672</v>
       </c>
@@ -6391,8 +6467,12 @@
       <c r="G2" s="5" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" t="str">
+        <f>_xlfn.CONCAT("insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('",A2,"','",C2,"','",D2,"','",E2,"');")</f>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110032672','9110032672','ADESH TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>9110032672</v>
       </c>
@@ -6414,8 +6494,12 @@
       <c r="G3" s="5" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H66" si="0">_xlfn.CONCAT("insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('",A3,"','",C3,"','",D3,"','",E3,"');")</f>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110032672','9111344015','A.K.BROTHERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>9110032672</v>
       </c>
@@ -6437,8 +6521,12 @@
       <c r="G4" s="5" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110032672','9111066282','NARAIN CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>9110097794</v>
       </c>
@@ -6460,8 +6548,12 @@
       <c r="G5" s="5" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110097794','9110097794','AJAY PAINT AND HARDWARE STORES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>9110033143</v>
       </c>
@@ -6483,8 +6575,12 @@
       <c r="G6" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111395954','ADARSH BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>9110033143</v>
       </c>
@@ -6506,8 +6602,12 @@
       <c r="G7" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9110033143','AKASH ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>9110033143</v>
       </c>
@@ -6529,8 +6629,12 @@
       <c r="G8" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111341619','SHRI LAXMIPATI BALAJEE INTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>9110033143</v>
       </c>
@@ -6552,8 +6656,12 @@
       <c r="G9" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111396089','SHIV SHAKTI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9110033143</v>
       </c>
@@ -6575,8 +6683,12 @@
       <c r="G10" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111393309','SHIVAM BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>9110033143</v>
       </c>
@@ -6598,8 +6710,12 @@
       <c r="G11" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111450847','PRITAM BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>9110033143</v>
       </c>
@@ -6621,8 +6737,12 @@
       <c r="G12" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111450845','PURVANCHAL STEEL UDYOG','VARANASI');</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>9110033143</v>
       </c>
@@ -6644,8 +6764,12 @@
       <c r="G13" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111395959','NAV DURGA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>9110033143</v>
       </c>
@@ -6667,8 +6791,12 @@
       <c r="G14" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111395237','ARVIND CHAUBEY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9110033143</v>
       </c>
@@ -6690,8 +6818,12 @@
       <c r="G15" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111282887','AYUSH ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>9110033143</v>
       </c>
@@ -6713,8 +6845,12 @@
       <c r="G16" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111395238','KHUSHI ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>9110033143</v>
       </c>
@@ -6736,8 +6872,12 @@
       <c r="G17" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111441930','DILEEP KUMAR JAISWAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>9110033143</v>
       </c>
@@ -6759,8 +6899,12 @@
       <c r="G18" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111486627','AZEEM BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>9110033143</v>
       </c>
@@ -6782,8 +6926,12 @@
       <c r="G19" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111153859','SUNIL BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>9110033143</v>
       </c>
@@ -6805,8 +6953,12 @@
       <c r="G20" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111482874','MAA AMBE BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>9110033143</v>
       </c>
@@ -6828,8 +6980,12 @@
       <c r="G21" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111249789','SHRI BALAJI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>9110033143</v>
       </c>
@@ -6851,8 +7007,12 @@
       <c r="G22" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111437592','RAJNATH BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>9110033143</v>
       </c>
@@ -6874,8 +7034,12 @@
       <c r="G23" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111393307','MISHRA BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>9110033143</v>
       </c>
@@ -6897,8 +7061,12 @@
       <c r="G24" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111441929','SATYANANT ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>9110033143</v>
       </c>
@@ -6920,8 +7088,12 @@
       <c r="G25" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111396088','SENGER BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>9110033143</v>
       </c>
@@ -6943,8 +7115,12 @@
       <c r="G26" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111393308','BAJRANG HARDWARE &amp; BUILDING MATERIA','VARANASI');</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>9110033143</v>
       </c>
@@ -6966,8 +7142,12 @@
       <c r="G27" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033143','9111441928','SADGURU ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>9110117683</v>
       </c>
@@ -6989,8 +7169,12 @@
       <c r="G28" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9111439952','OM BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>9110117683</v>
       </c>
@@ -7012,8 +7196,12 @@
       <c r="G29" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9111490755','S K ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>9110117683</v>
       </c>
@@ -7035,8 +7223,12 @@
       <c r="G30" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9111472814','CHIRANJEEVI CONSTRUCTION','VARANASI');</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>9110117683</v>
       </c>
@@ -7058,8 +7250,12 @@
       <c r="G31" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9110117683','AKK TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>9110117683</v>
       </c>
@@ -7081,8 +7277,12 @@
       <c r="G32" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9111396158','AMBA TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>9110117683</v>
       </c>
@@ -7104,8 +7304,12 @@
       <c r="G33" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9111372887','BHARAT ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>9110117683</v>
       </c>
@@ -7127,8 +7331,12 @@
       <c r="G34" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9111367518','NASEER KHAN','VARANASI');</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>9110117683</v>
       </c>
@@ -7150,8 +7358,12 @@
       <c r="G35" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9111369361','SHYAMA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>9110117683</v>
       </c>
@@ -7173,8 +7385,12 @@
       <c r="G36" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9111470298','AVANI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>9110117683</v>
       </c>
@@ -7196,8 +7412,12 @@
       <c r="G37" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9111388702','KHAN BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>9110117683</v>
       </c>
@@ -7219,8 +7439,12 @@
       <c r="G38" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9111356849','SHUBHI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>9110117683</v>
       </c>
@@ -7242,8 +7466,12 @@
       <c r="G39" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9111389988','VARANASI CONCRETE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>9110117683</v>
       </c>
@@ -7265,8 +7493,12 @@
       <c r="G40" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110117683','9111388703','KHAN AND SONS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>9110235610</v>
       </c>
@@ -7288,8 +7520,12 @@
       <c r="G41" s="5" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H41" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110235610','9110235610','AMAN BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>9110221017</v>
       </c>
@@ -7311,8 +7547,12 @@
       <c r="G42" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H42" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110221017','9111480449','OM SAKSHI TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>9110221017</v>
       </c>
@@ -7334,8 +7574,12 @@
       <c r="G43" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110221017','9110221017','AMAR CONSTRUCTIONS AND SUPPLIER','VARANASI');</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>9110221017</v>
       </c>
@@ -7357,8 +7601,12 @@
       <c r="G44" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H44" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110221017','9111463830','A P BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>9110221017</v>
       </c>
@@ -7380,8 +7628,12 @@
       <c r="G45" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H45" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110221017','9111489817','DHEER ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>9110033203</v>
       </c>
@@ -7403,8 +7655,12 @@
       <c r="G46" s="5" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H46" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033203','9111348632','SHYAM LAL JINDAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>9110033203</v>
       </c>
@@ -7426,8 +7682,12 @@
       <c r="G47" s="5" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H47" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033203','9110033203','ANJALI ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>9110033203</v>
       </c>
@@ -7449,8 +7709,12 @@
       <c r="G48" s="5" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H48" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033203','9111394841','VERMA LIME STORE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>9110202061</v>
       </c>
@@ -7472,8 +7736,12 @@
       <c r="G49" s="5" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H49" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110202061','9110202061','ANKIT BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>9110208385</v>
       </c>
@@ -7495,8 +7763,12 @@
       <c r="G50" s="5" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H50" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110208385','9110208385','ANUJ TRADING COMPANY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>9110208385</v>
       </c>
@@ -7518,8 +7790,12 @@
       <c r="G51" s="5" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H51" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110208385','9111442997','MAA SANKTHA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>9110207934</v>
       </c>
@@ -7541,8 +7817,12 @@
       <c r="G52" s="5" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H52" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110207934','9110207934','AWANTI CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>9110207934</v>
       </c>
@@ -7564,8 +7844,12 @@
       <c r="G53" s="5" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H53" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110207934','9111414832','DINESH KUMAR VERMA','VARANASI');</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>9110207934</v>
       </c>
@@ -7587,8 +7871,12 @@
       <c r="G54" s="5" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H54" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110207934','9111443375','SAROJ DEVI','VARANASI');</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>9110217758</v>
       </c>
@@ -7610,8 +7898,12 @@
       <c r="G55" s="5" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110217758','9110217758','AYUSH TRADING COMPANY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>9110235576</v>
       </c>
@@ -7633,8 +7925,12 @@
       <c r="G56" s="5" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H56" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110235576','9110235576','BEMISHAL CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>9110232851</v>
       </c>
@@ -7656,8 +7952,12 @@
       <c r="G57" s="5" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110232851','9110232851','BHAGIRATHI CONSTRUCTION AND SUPPLIE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>9110092659</v>
       </c>
@@ -7679,8 +7979,12 @@
       <c r="G58" s="5" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H58" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110092659','9110092659','BHOLE NATH ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>9110033101</v>
       </c>
@@ -7702,8 +8006,12 @@
       <c r="G59" s="5" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033101','9111063700','KAMAKYHA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>9110033101</v>
       </c>
@@ -7725,8 +8033,12 @@
       <c r="G60" s="5" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H60" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033101','9111311873','KHALIK BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>9110033101</v>
       </c>
@@ -7748,8 +8060,12 @@
       <c r="G61" s="5" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H61" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033101','9110033101','BIRASAN ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>9110187050</v>
       </c>
@@ -7771,8 +8087,12 @@
       <c r="G62" s="5" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H62" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110187050','9111480498','AARADHY BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>9110187050</v>
       </c>
@@ -7794,8 +8114,12 @@
       <c r="G63" s="5" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H63" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110187050','9110187050','DAYAL TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>9110187050</v>
       </c>
@@ -7817,8 +8141,12 @@
       <c r="G64" s="5" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H64" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110187050','9111434373','R S CONSTRUCTION AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>9110131504</v>
       </c>
@@ -7840,8 +8168,12 @@
       <c r="G65" s="5" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H65" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110131504','9111447527','HARSHIT ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>9110131504</v>
       </c>
@@ -7863,8 +8195,12 @@
       <c r="G66" s="5" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H66" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110131504','9110131504','DEVARSHI ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>9110131504</v>
       </c>
@@ -7886,8 +8222,12 @@
       <c r="G67" s="5" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H67" t="str">
+        <f t="shared" ref="H67:H130" si="1">_xlfn.CONCAT("insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('",A67,"','",C67,"','",D67,"','",E67,"');")</f>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110131504','9111330368','VERMA CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>9110131504</v>
       </c>
@@ -7909,8 +8249,12 @@
       <c r="G68" s="5" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H68" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110131504','9111066186','CHANDEL ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>9110131504</v>
       </c>
@@ -7932,8 +8276,12 @@
       <c r="G69" s="5" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H69" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110131504','9111432362','VIBHA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>9110131504</v>
       </c>
@@ -7955,8 +8303,12 @@
       <c r="G70" s="5" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H70" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110131504','9111392099','GAURAV TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>9110131504</v>
       </c>
@@ -7978,8 +8330,12 @@
       <c r="G71" s="5" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H71" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110131504','9111205007','S KUMAR BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>9110131504</v>
       </c>
@@ -8001,8 +8357,12 @@
       <c r="G72" s="5" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H72" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110131504','9111299352','POORNIMA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>9110131504</v>
       </c>
@@ -8024,8 +8384,12 @@
       <c r="G73" s="5" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H73" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110131504','9111408192','OM ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>9110204851</v>
       </c>
@@ -8047,8 +8411,12 @@
       <c r="G74" s="5" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H74" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110204851','9110204851','DIVYANSH BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>9110209421</v>
       </c>
@@ -8070,8 +8438,12 @@
       <c r="G75" s="5" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H75" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110209421','9111452654','SHIDRATH ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>9110209421</v>
       </c>
@@ -8093,8 +8465,12 @@
       <c r="G76" s="5" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H76" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110209421','9111489795','VISHAL BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>9110209421</v>
       </c>
@@ -8116,8 +8492,12 @@
       <c r="G77" s="5" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H77" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110209421','9110209421','FVS TRADING CORPORATION','VARANASI');</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>9110209421</v>
       </c>
@@ -8139,8 +8519,12 @@
       <c r="G78" s="5" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H78" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110209421','9111470084','SHIVAM SINGH','VARANASI');</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>9110144134</v>
       </c>
@@ -8162,8 +8546,12 @@
       <c r="G79" s="5" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H79" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110144134','9110144134','G S TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>9110144134</v>
       </c>
@@ -8185,8 +8573,12 @@
       <c r="G80" s="5" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H80" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110144134','9111400344','ABRAR KHAN','VARANASI');</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>9110144134</v>
       </c>
@@ -8208,8 +8600,12 @@
       <c r="G81" s="5" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H81" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110144134','9111413749','ABHAY YADAV','VARANASI');</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>9110184692</v>
       </c>
@@ -8231,8 +8627,12 @@
       <c r="G82" s="5" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H82" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110184692','9110184692','GEETA BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>9110178852</v>
       </c>
@@ -8254,8 +8654,12 @@
       <c r="G83" s="5" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H83" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110178852','9110178852','HARSH CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>9110173220</v>
       </c>
@@ -8277,8 +8681,12 @@
       <c r="G84" s="5" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H84" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110173220','9110173220','HEMANT ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>9110173220</v>
       </c>
@@ -8300,8 +8708,12 @@
       <c r="G85" s="5" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H85" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110173220','9111489818','JAI AMBEY TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>9110206595</v>
       </c>
@@ -8323,8 +8735,12 @@
       <c r="G86" s="5" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H86" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206595','9110206595','JAY AMBEY ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>9110206595</v>
       </c>
@@ -8346,8 +8762,12 @@
       <c r="G87" s="5" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H87" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206595','9111458482','R R CHAURASHIYA BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>9110202060</v>
       </c>
@@ -8369,8 +8789,12 @@
       <c r="G88" s="5" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H88" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110202060','9110202060','JYOTI BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>9110202060</v>
       </c>
@@ -8392,8 +8816,12 @@
       <c r="G89" s="5" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H89" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110202060','9111456432','PARVATI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>9110171676</v>
       </c>
@@ -8415,8 +8843,12 @@
       <c r="G90" s="5" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H90" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110171676','9110171676','KAMAL ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>9110236010</v>
       </c>
@@ -8438,8 +8870,12 @@
       <c r="G91" s="5" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H91" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110236010','9110236010','KESHARWANI AGENCIES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>9110170402</v>
       </c>
@@ -8461,8 +8897,12 @@
       <c r="G92" s="5" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H92" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110170402','9110170402','KOMAL ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>9110045030</v>
       </c>
@@ -8484,8 +8924,12 @@
       <c r="G93" s="5" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H93" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110045030','9110045030','KRIPA SHANKAR SINGH','VARANASI');</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>9110225636</v>
       </c>
@@ -8507,8 +8951,12 @@
       <c r="G94" s="5" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H94" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110225636','9110225636','KRIPA TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>9110205222</v>
       </c>
@@ -8530,8 +8978,12 @@
       <c r="G95" s="5" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H95" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110205222','9110205222','KRISHNA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>9110205222</v>
       </c>
@@ -8553,8 +9005,12 @@
       <c r="G96" s="5" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H96" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110205222','9111439951','NARAYAN ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>9110205222</v>
       </c>
@@ -8576,8 +9032,12 @@
       <c r="G97" s="5" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H97" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110205222','9111437590','AKANCHHA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>9110146501</v>
       </c>
@@ -8599,8 +9059,12 @@
       <c r="G98" s="5" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H98" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110146501','9110146501','KRISHNA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>9110203758</v>
       </c>
@@ -8622,8 +9086,12 @@
       <c r="G99" s="5" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H99" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110203758','9110203758','KRV ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>9110234954</v>
       </c>
@@ -8645,8 +9113,12 @@
       <c r="G100" s="5" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H100" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110234954','9110234954','M K ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
         <v>9110190952</v>
       </c>
@@ -8668,8 +9140,12 @@
       <c r="G101" s="5" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H101" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110190952','9110190952','MAA VAISHNO ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>9110172831</v>
       </c>
@@ -8691,8 +9167,12 @@
       <c r="G102" s="5" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H102" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110172831','9111456645','PATEL ENTERPRISE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>9110172831</v>
       </c>
@@ -8714,8 +9194,12 @@
       <c r="G103" s="5" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H103" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110172831','9111480441','JAI MAA KALI HARDWARE SANITARY AND','VARANASI');</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>9110172831</v>
       </c>
@@ -8737,8 +9221,12 @@
       <c r="G104" s="5" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H104" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110172831','9111450846','ARPIT ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
         <v>9110172831</v>
       </c>
@@ -8760,8 +9248,12 @@
       <c r="G105" s="5" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H105" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110172831','9110172831','MAA VASHINO HARDWARE BUILDING','VARANASI');</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>9110172831</v>
       </c>
@@ -8783,8 +9275,12 @@
       <c r="G106" s="5" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H106" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110172831','9111382007','KARAN CONSTRUCTION','VARANASI');</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>9110130915</v>
       </c>
@@ -8806,8 +9302,12 @@
       <c r="G107" s="5" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H107" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110130915','9110130915','MAHARAJ JI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>9110187741</v>
       </c>
@@ -8829,8 +9329,12 @@
       <c r="G108" s="5" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H108" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110187741','9110187741','MAHAVEER ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>9110092656</v>
       </c>
@@ -8852,8 +9356,12 @@
       <c r="G109" s="5" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H109" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110092656','9110092656','MALTI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
         <v>9110208384</v>
       </c>
@@ -8875,8 +9383,12 @@
       <c r="G110" s="5" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H110" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110208384','9111490758','GAUTAMI STEELS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
         <v>9110208384</v>
       </c>
@@ -8898,8 +9410,12 @@
       <c r="G111" s="5" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H111" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110208384','9110208384','MATICOTECH INFRASTRUCTURE PVT LTD','VARANASI');</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
         <v>9110217209</v>
       </c>
@@ -8921,8 +9437,12 @@
       <c r="G112" s="5" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H112" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110217209','9111452655','JAMUNA PRASAD GAYA PRASAD','VARANASI');</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>9110217209</v>
       </c>
@@ -8944,8 +9464,12 @@
       <c r="G113" s="5" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H113" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110217209','9110217209','MISHRA BUILDING SOLUTIONS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>9110231172</v>
       </c>
@@ -8967,8 +9491,12 @@
       <c r="G114" s="5" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H114" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110231172','9110231172','MOURYA ENTERRPISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>9110228566</v>
       </c>
@@ -8990,8 +9518,12 @@
       <c r="G115" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H115" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111432573','ROHIT CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>9110228566</v>
       </c>
@@ -9013,8 +9545,12 @@
       <c r="G116" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H116" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9110228566','NEW PRADEEP STEELS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>9110228566</v>
       </c>
@@ -9036,8 +9572,12 @@
       <c r="G117" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H117" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111343558','SIDDHART TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>9110228566</v>
       </c>
@@ -9059,8 +9599,12 @@
       <c r="G118" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H118" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111424087','VIVEK CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>9110228566</v>
       </c>
@@ -9082,8 +9626,12 @@
       <c r="G119" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H119" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111380045','GOPAL ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
         <v>9110228566</v>
       </c>
@@ -9105,8 +9653,12 @@
       <c r="G120" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H120" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111346005','KRISHNA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
         <v>9110228566</v>
       </c>
@@ -9128,8 +9680,12 @@
       <c r="G121" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H121" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111188823','FRIENDS ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>9110228566</v>
       </c>
@@ -9151,8 +9707,12 @@
       <c r="G122" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H122" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111203452','JAISWAL CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>9110228566</v>
       </c>
@@ -9174,8 +9734,12 @@
       <c r="G123" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H123" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111331033','MAA BAGESHWARI ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
         <v>9110228566</v>
       </c>
@@ -9197,8 +9761,12 @@
       <c r="G124" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H124" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111345770','GAURAV ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>9110228566</v>
       </c>
@@ -9220,8 +9788,12 @@
       <c r="G125" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H125" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111346004','AGRAHARI CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
         <v>9110228566</v>
       </c>
@@ -9243,8 +9815,12 @@
       <c r="G126" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H126" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111394842','BABA KINARAM TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="4">
         <v>9110228566</v>
       </c>
@@ -9266,8 +9842,12 @@
       <c r="G127" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H127" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111486628','ADITI CONSTRUCTION','VARANASI');</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
         <v>9110228566</v>
       </c>
@@ -9289,8 +9869,12 @@
       <c r="G128" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H128" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111236126','SUNIL KUMAR','VARANASI');</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
         <v>9110228566</v>
       </c>
@@ -9312,8 +9896,12 @@
       <c r="G129" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H129" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111392096','SANJANA STEELS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
         <v>9110228566</v>
       </c>
@@ -9335,8 +9923,12 @@
       <c r="G130" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H130" t="str">
+        <f t="shared" si="1"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111416945','SHUBH BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
         <v>9110228566</v>
       </c>
@@ -9358,8 +9950,12 @@
       <c r="G131" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H131" t="str">
+        <f t="shared" ref="H131:H194" si="2">_xlfn.CONCAT("insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('",A131,"','",C131,"','",D131,"','",E131,"');")</f>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111418150','MAYANK TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
         <v>9110228566</v>
       </c>
@@ -9381,8 +9977,12 @@
       <c r="G132" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H132" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111475008','HAYAN TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
         <v>9110228566</v>
       </c>
@@ -9404,8 +10004,12 @@
       <c r="G133" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H133" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111188825','SALIM BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
         <v>9110228566</v>
       </c>
@@ -9427,8 +10031,12 @@
       <c r="G134" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H134" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111456418','JAI MAA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <v>9110228566</v>
       </c>
@@ -9450,8 +10058,12 @@
       <c r="G135" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H135" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111410766','ANKUR AGRAHARI','VARANASI');</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <v>9110228566</v>
       </c>
@@ -9473,8 +10085,12 @@
       <c r="G136" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H136" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111378581','GANPATI ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <v>9110228566</v>
       </c>
@@ -9496,8 +10112,12 @@
       <c r="G137" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H137" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111238061','ALOK KUMAR GUPTA','VARANASI');</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <v>9110228566</v>
       </c>
@@ -9519,8 +10139,12 @@
       <c r="G138" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H138" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111188822','RAM SUMER &amp; SONS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <v>9110228566</v>
       </c>
@@ -9542,8 +10166,12 @@
       <c r="G139" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H139" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111449028','KRISHNA TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
         <v>9110228566</v>
       </c>
@@ -9565,8 +10193,12 @@
       <c r="G140" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H140" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111380046','HARE KRISHNA CEMENT STORE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <v>9110228566</v>
       </c>
@@ -9588,8 +10220,12 @@
       <c r="G141" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H141" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111437591','INDRASANI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
         <v>9110228566</v>
       </c>
@@ -9611,8 +10247,12 @@
       <c r="G142" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H142" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111271757','ASHUTOSH ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
         <v>9110228566</v>
       </c>
@@ -9634,8 +10274,12 @@
       <c r="G143" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H143" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228566','9111190464','SHIV BUILDING MATERILS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <v>9110200556</v>
       </c>
@@ -9657,8 +10301,12 @@
       <c r="G144" s="5" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H144" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110200556','9110200556','OM BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
         <v>9110170948</v>
       </c>
@@ -9680,8 +10328,12 @@
       <c r="G145" s="5" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H145" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110170948','9110170948','OM SHIV BHOLE BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
         <v>9110234216</v>
       </c>
@@ -9703,8 +10355,12 @@
       <c r="G146" s="5" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H146" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110234216','9110234216','OM SHREE SAI NATH ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
         <v>9110033198</v>
       </c>
@@ -9726,8 +10382,12 @@
       <c r="G147" s="5" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H147" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033198','9110033198','OM TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>9110220921</v>
       </c>
@@ -9749,8 +10409,12 @@
       <c r="G148" s="5" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H148" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110220921','9111460257','SHUBHI TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
         <v>9110220921</v>
       </c>
@@ -9772,8 +10436,12 @@
       <c r="G149" s="5" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H149" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110220921','9110220921','PARTH BUILDCON','VARANASI');</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="4">
         <v>9110178792</v>
       </c>
@@ -9795,8 +10463,12 @@
       <c r="G150" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H150" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110178792','9110178792','PATHAK BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="4">
         <v>9110237589</v>
       </c>
@@ -9818,8 +10490,12 @@
       <c r="G151" s="5" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H151" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110237589','9110237589','PAWAN ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="4">
         <v>9110046614</v>
       </c>
@@ -9841,8 +10517,12 @@
       <c r="G152" s="5" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H152" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110046614','9111150322','SHASHANK CEMENT AGENCEY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="4">
         <v>9110046614</v>
       </c>
@@ -9864,8 +10544,12 @@
       <c r="G153" s="5" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H153" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110046614','9111150321','JAISWAL CEMENT STORE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="4">
         <v>9110046614</v>
       </c>
@@ -9887,8 +10571,12 @@
       <c r="G154" s="5" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H154" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110046614','9111169467','JAI PRAKASH SINGH','VARANASI');</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="4">
         <v>9110046614</v>
       </c>
@@ -9910,8 +10598,12 @@
       <c r="G155" s="5" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H155" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110046614','9111169457','JP BUILDERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
         <v>9110046614</v>
       </c>
@@ -9933,8 +10625,12 @@
       <c r="G156" s="5" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H156" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110046614','9111367092','ADITYA RAJ JAISWAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="4">
         <v>9110046614</v>
       </c>
@@ -9956,8 +10652,12 @@
       <c r="G157" s="5" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H157" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110046614','9111169452','PUJA CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="4">
         <v>9110046614</v>
       </c>
@@ -9979,8 +10679,12 @@
       <c r="G158" s="5" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H158" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110046614','9110046614','PURWAR CEMENT BHANDAR','VARANASI');</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="4">
         <v>9110033210</v>
       </c>
@@ -10002,8 +10706,12 @@
       <c r="G159" s="5" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H159" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033210','9110033210','R K BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="4">
         <v>9110225594</v>
       </c>
@@ -10025,8 +10733,12 @@
       <c r="G160" s="5" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H160" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110225594','9111472813','JYOTSANA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="4">
         <v>9110225594</v>
       </c>
@@ -10048,8 +10760,12 @@
       <c r="G161" s="5" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H161" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110225594','9110225594','RAGINI ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="4">
         <v>9110225594</v>
       </c>
@@ -10071,8 +10787,12 @@
       <c r="G162" s="5" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H162" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110225594','9111472812','MAA GAYATRI TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="4">
         <v>9110070000</v>
       </c>
@@ -10094,8 +10814,12 @@
       <c r="G163" s="5" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H163" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110070000','9110070000','RAJARAM OMPRAKASH IRON STORE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="4">
         <v>9110033157</v>
       </c>
@@ -10117,8 +10841,12 @@
       <c r="G164" s="5" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H164" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033157','9110033157','ROSHAN CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="4">
         <v>9110235599</v>
       </c>
@@ -10140,8 +10868,12 @@
       <c r="G165" s="5" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H165" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110235599','9110235599','ROYAL TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="4">
         <v>9110180027</v>
       </c>
@@ -10163,8 +10895,12 @@
       <c r="G166" s="5" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H166" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110180027','9110180027','S K ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
         <v>9110206768</v>
       </c>
@@ -10186,8 +10922,12 @@
       <c r="G167" s="5" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H167" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206768','9111471419','PATEL BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="4">
         <v>9110206768</v>
       </c>
@@ -10209,8 +10949,12 @@
       <c r="G168" s="5" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H168" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206768','9111207346','SONU BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="4">
         <v>9110206768</v>
       </c>
@@ -10232,8 +10976,12 @@
       <c r="G169" s="5" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H169" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206768','9111435449','PATEL KHADH BHANDAR','VARANASI');</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="4">
         <v>9110206768</v>
       </c>
@@ -10255,8 +11003,12 @@
       <c r="G170" s="5" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H170" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206768','9110206768','SAHU TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="4">
         <v>9110093690</v>
       </c>
@@ -10278,8 +11030,12 @@
       <c r="G171" s="5" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H171" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110093690','9110093690','SAI CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="4">
         <v>9110078716</v>
       </c>
@@ -10301,8 +11057,12 @@
       <c r="G172" s="5" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H172" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110078716','9110078716','SAMRAT IRON STORES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="4">
         <v>9110033156</v>
       </c>
@@ -10324,8 +11084,12 @@
       <c r="G173" s="5" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H173" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033156','9110033156','SATYA NARAIN CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="4">
         <v>9110033205</v>
       </c>
@@ -10347,8 +11111,12 @@
       <c r="G174" s="5" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H174" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033205','9110033205','SHIVA CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="4">
         <v>9110033207</v>
       </c>
@@ -10370,8 +11138,12 @@
       <c r="G175" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H175" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9110033207','SHIVAM CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="4">
         <v>9110033207</v>
       </c>
@@ -10393,8 +11165,12 @@
       <c r="G176" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H176" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111463014','ADARSH BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="4">
         <v>9110033207</v>
       </c>
@@ -10416,8 +11192,12 @@
       <c r="G177" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H177" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111478154','ANNAPURNA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
         <v>9110033207</v>
       </c>
@@ -10439,8 +11219,12 @@
       <c r="G178" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H178" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111462090','RAJBALI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="4">
         <v>9110033207</v>
       </c>
@@ -10462,8 +11246,12 @@
       <c r="G179" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H179" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111416890','RAKSHAK BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="4">
         <v>9110033207</v>
       </c>
@@ -10485,8 +11273,12 @@
       <c r="G180" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H180" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111304913','SWASHTIK BUILDING M.','VARANASI');</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="4">
         <v>9110033207</v>
       </c>
@@ -10508,8 +11300,12 @@
       <c r="G181" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H181" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111442994','NILKANTH BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="4">
         <v>9110033207</v>
       </c>
@@ -10531,8 +11327,12 @@
       <c r="G182" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H182" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111304910','VIKAS CEMENT AGENCIES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="4">
         <v>9110033207</v>
       </c>
@@ -10554,8 +11354,12 @@
       <c r="G183" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H183" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111435451','PATEL BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="4">
         <v>9110033207</v>
       </c>
@@ -10577,8 +11381,12 @@
       <c r="G184" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H184" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111066207','NEW PATEL CEMENT SALES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="4">
         <v>9110033207</v>
       </c>
@@ -10600,8 +11408,12 @@
       <c r="G185" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H185" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111364351','AVANISH CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="4">
         <v>9110033207</v>
       </c>
@@ -10623,8 +11435,12 @@
       <c r="G186" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H186" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111464761','A K ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="4">
         <v>9110033207</v>
       </c>
@@ -10646,8 +11462,12 @@
       <c r="G187" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H187" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111066230','RAJ BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="4">
         <v>9110033207</v>
       </c>
@@ -10669,8 +11489,12 @@
       <c r="G188" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H188" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111154857','RAJENDER CEMENT AGENCY.','VARANASI');</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
         <v>9110033207</v>
       </c>
@@ -10692,8 +11516,12 @@
       <c r="G189" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H189" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111063755','ANAND BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="4">
         <v>9110033207</v>
       </c>
@@ -10715,8 +11543,12 @@
       <c r="G190" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H190" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111470083','OM SAI ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="4">
         <v>9110033207</v>
       </c>
@@ -10738,8 +11570,12 @@
       <c r="G191" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H191" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111330948','AARAV ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="4">
         <v>9110033207</v>
       </c>
@@ -10761,8 +11597,12 @@
       <c r="G192" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H192" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111315471','PAL BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="4">
         <v>9110033207</v>
       </c>
@@ -10784,8 +11624,12 @@
       <c r="G193" s="5" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H193" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033207','9111063797','PUJA BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="4">
         <v>9110159541</v>
       </c>
@@ -10807,8 +11651,12 @@
       <c r="G194" s="5" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H194" t="str">
+        <f t="shared" si="2"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110159541','9111371492','SRI JAGDAMBA CEMENT STORE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="4">
         <v>9110159541</v>
       </c>
@@ -10830,8 +11678,12 @@
       <c r="G195" s="5" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H195" t="str">
+        <f t="shared" ref="H195:H258" si="3">_xlfn.CONCAT("insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('",A195,"','",C195,"','",D195,"','",E195,"');")</f>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110159541','9111449234','PRADEEP KUMAR','CHANDAULI');</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="4">
         <v>9110159541</v>
       </c>
@@ -10853,8 +11705,12 @@
       <c r="G196" s="5" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H196" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110159541','9111413909','PANKAJ KUMAR','VARANASI');</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="4">
         <v>9110159541</v>
       </c>
@@ -10876,8 +11732,12 @@
       <c r="G197" s="5" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H197" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110159541','9110159541','SHREE BALAJI ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="4">
         <v>9110235580</v>
       </c>
@@ -10899,8 +11759,12 @@
       <c r="G198" s="5" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H198" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110235580','9110235580','SHREE MAHADEV BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="4">
         <v>9110033213</v>
       </c>
@@ -10922,8 +11786,12 @@
       <c r="G199" s="5" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H199" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033213','9110033213','SHREE RAM IRON STORES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
         <v>9110206767</v>
       </c>
@@ -10945,8 +11813,12 @@
       <c r="G200" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H200" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9110206767','SHREE RAM STEEL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="4">
         <v>9110206767</v>
       </c>
@@ -10968,8 +11840,12 @@
       <c r="G201" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H201" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111441931','DEEPAK IRON STORE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="4">
         <v>9110206767</v>
       </c>
@@ -10991,8 +11867,12 @@
       <c r="G202" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H202" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111456089','DEEPAK CEMENT AND HARDWARE STORE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
         <v>9110206767</v>
       </c>
@@ -11014,8 +11894,12 @@
       <c r="G203" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H203" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111469058','JAIN ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
         <v>9110206767</v>
       </c>
@@ -11037,8 +11921,12 @@
       <c r="G204" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H204" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111488051','MARUTI BUILDING MATERIAL AND','VARANASI');</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
         <v>9110206767</v>
       </c>
@@ -11060,8 +11948,12 @@
       <c r="G205" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H205" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111480499','JAISWAL BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
         <v>9110206767</v>
       </c>
@@ -11083,8 +11975,12 @@
       <c r="G206" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H206" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111451366','DHIRENDRA KUMAR','VARANASI');</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
         <v>9110206767</v>
       </c>
@@ -11106,8 +12002,12 @@
       <c r="G207" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H207" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111442996','SINGH BROTHER CONSTRUCTION','VARANASI');</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
         <v>9110206767</v>
       </c>
@@ -11129,8 +12029,12 @@
       <c r="G208" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H208" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111470299','VIVEK ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
         <v>9110206767</v>
       </c>
@@ -11152,8 +12056,12 @@
       <c r="G209" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H209" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111445246','SETH BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
         <v>9110206767</v>
       </c>
@@ -11175,8 +12083,12 @@
       <c r="G210" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H210" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111449029','SHAURY CONSTRUCTION','VARANASI');</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
         <v>9110206767</v>
       </c>
@@ -11198,8 +12110,12 @@
       <c r="G211" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H211" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111441150','SHARDA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="4">
         <v>9110206767</v>
       </c>
@@ -11221,8 +12137,12 @@
       <c r="G212" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H212" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111480595','SKS ENTERPRISES','CHANDAULI');</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="4">
         <v>9110206767</v>
       </c>
@@ -11244,8 +12164,12 @@
       <c r="G213" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H213" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111453795','PRAVEEN PATHAK','VARANASI');</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="4">
         <v>9110206767</v>
       </c>
@@ -11267,8 +12191,12 @@
       <c r="G214" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H214" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111490757','RAI TRADING COMPANY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="4">
         <v>9110206767</v>
       </c>
@@ -11290,8 +12218,12 @@
       <c r="G215" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H215" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111456429','ASHA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
         <v>9110206767</v>
       </c>
@@ -11313,8 +12245,12 @@
       <c r="G216" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H216" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111442995','AYUSH SHARMA','VARANASI');</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
         <v>9110206767</v>
       </c>
@@ -11336,8 +12272,12 @@
       <c r="G217" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H217" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110206767','9111439938','VIDHAN CONSTRUCTION','VARANASI');</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
         <v>9110234300</v>
       </c>
@@ -11359,8 +12299,12 @@
       <c r="G218" s="5" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H218" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110234300','9110234300','SHRI GANPATI INFRATECH','VARANASI');</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
         <v>9110224954</v>
       </c>
@@ -11382,8 +12326,12 @@
       <c r="G219" s="5" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H219" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110224954','9111474990','MAA DURGA TREADING','VARANASI');</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
         <v>9110224954</v>
       </c>
@@ -11405,8 +12353,12 @@
       <c r="G220" s="5" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H220" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110224954','9110224954','SHRI RAM ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
         <v>9110224954</v>
       </c>
@@ -11428,8 +12380,12 @@
       <c r="G221" s="5" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H221" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110224954','9111486606','DHANSHRI ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
         <v>9110183722</v>
       </c>
@@ -11451,8 +12407,12 @@
       <c r="G222" s="5" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H222" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110183722','9110183722','SHRI SIDDHI VINAYAK BUILDING','VARANASI');</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
         <v>9110183722</v>
       </c>
@@ -11474,8 +12434,12 @@
       <c r="G223" s="5" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H223" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110183722','9111394846','JAGDISH NARAYAN','VARANASI');</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="4">
         <v>9110235624</v>
       </c>
@@ -11497,8 +12461,12 @@
       <c r="G224" s="5" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H224" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110235624','9110235624','SINGH BROTHERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
         <v>9110220933</v>
       </c>
@@ -11520,8 +12488,12 @@
       <c r="G225" s="5" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H225" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110220933','9110220933','SN INFRA MARKET','VARANASI');</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
         <v>9110228028</v>
       </c>
@@ -11543,8 +12515,12 @@
       <c r="G226" s="5" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H226" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110228028','9110228028','SRI MAHADEV ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
         <v>9110166533</v>
       </c>
@@ -11566,8 +12542,12 @@
       <c r="G227" s="5" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H227" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110166533','9110166533','SUMITRA TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
         <v>9110166533</v>
       </c>
@@ -11589,8 +12569,12 @@
       <c r="G228" s="5" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H228" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110166533','9111393559','PANKAJ JAISWAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
         <v>9110166533</v>
       </c>
@@ -11612,8 +12596,12 @@
       <c r="G229" s="5" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H229" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110166533','9111489791','MAA ANNAPURNA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="4">
         <v>9110166533</v>
       </c>
@@ -11635,8 +12623,12 @@
       <c r="G230" s="5" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H230" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110166533','9111488050','AMAN BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
         <v>9110166533</v>
       </c>
@@ -11658,8 +12650,12 @@
       <c r="G231" s="5" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H231" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110166533','9111456150','SATISH KUMAR JAISWAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
         <v>9110166533</v>
       </c>
@@ -11681,8 +12677,12 @@
       <c r="G232" s="5" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H232" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110166533','9111375229','RAMESH CHANDRA TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
         <v>9110166533</v>
       </c>
@@ -11704,8 +12704,12 @@
       <c r="G233" s="5" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H233" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110166533','9111451270','DASHARATH KUMAR RAI','VARANASI');</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
         <v>9110068757</v>
       </c>
@@ -11727,8 +12731,12 @@
       <c r="G234" s="5" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H234" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110068757','9110068757','SUNDER CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
         <v>9110188732</v>
       </c>
@@ -11750,8 +12758,12 @@
       <c r="G235" s="5" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H235" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110188732','9110188732','VIDHYA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="4">
         <v>9110188732</v>
       </c>
@@ -11773,8 +12785,12 @@
       <c r="G236" s="5" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H236" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110188732','9111400343','VIDYA STEEL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
         <v>9110162175</v>
       </c>
@@ -11796,8 +12812,12 @@
       <c r="G237" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H237" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9110162175','VIJAY SHANKAR CONSTRUCTION','VARANASI');</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
         <v>9110162175</v>
       </c>
@@ -11819,8 +12839,12 @@
       <c r="G238" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H238" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111396267','OM PRAKASH','VARANASI');</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
         <v>9110162175</v>
       </c>
@@ -11842,8 +12866,12 @@
       <c r="G239" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H239" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111367520','KHUSHBOO BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
         <v>9110162175</v>
       </c>
@@ -11865,8 +12893,12 @@
       <c r="G240" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H240" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111475713','MAYA MISHRA','VARANASI');</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
         <v>9110162175</v>
       </c>
@@ -11888,8 +12920,12 @@
       <c r="G241" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H241" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111392094','AVI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
         <v>9110162175</v>
       </c>
@@ -11911,8 +12947,12 @@
       <c r="G242" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H242" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111367519','NEW MAA SHITLA BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
         <v>9110162175</v>
       </c>
@@ -11934,8 +12974,12 @@
       <c r="G243" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H243" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111382006','AMAN BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
         <v>9110162175</v>
       </c>
@@ -11957,8 +13001,12 @@
       <c r="G244" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H244" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111448528','OM TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
         <v>9110162175</v>
       </c>
@@ -11980,8 +13028,12 @@
       <c r="G245" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H245" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111409381','RIDDHI SIDDHI TRADING','VARANASI');</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
         <v>9110162175</v>
       </c>
@@ -12003,8 +13055,12 @@
       <c r="G246" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H246" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111369360','BABA BAIJNATH ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
         <v>9110162175</v>
       </c>
@@ -12026,8 +13082,12 @@
       <c r="G247" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H247" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111434374','KEDAR BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
         <v>9110162175</v>
       </c>
@@ -12049,8 +13109,12 @@
       <c r="G248" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H248" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111404209','KRISHNA BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
         <v>9110162175</v>
       </c>
@@ -12072,8 +13136,12 @@
       <c r="G249" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H249" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111448487','KIRAN BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
         <v>9110162175</v>
       </c>
@@ -12095,8 +13163,12 @@
       <c r="G250" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H250" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111367522','NITISH YADAV','VARANASI');</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
         <v>9110162175</v>
       </c>
@@ -12118,8 +13190,12 @@
       <c r="G251" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H251" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111457767','SHIV SHAKTI ASSOCIATE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
         <v>9110162175</v>
       </c>
@@ -12141,8 +13217,12 @@
       <c r="G252" s="5" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H252" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110162175','9111373717','TARA DEVI','VARANASI');</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
         <v>9110145353</v>
       </c>
@@ -12164,8 +13244,12 @@
       <c r="G253" s="5" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H253" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110145353','9110145353','VINAY BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
         <v>9110033145</v>
       </c>
@@ -12187,8 +13271,12 @@
       <c r="G254" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H254" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111449027','TIRUPATI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
         <v>9110033145</v>
       </c>
@@ -12210,8 +13298,12 @@
       <c r="G255" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H255" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111457222','CHANDAN BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
         <v>9110033145</v>
       </c>
@@ -12233,8 +13325,12 @@
       <c r="G256" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H256" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111383616','SHIVAM ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
         <v>9110033145</v>
       </c>
@@ -12256,8 +13352,12 @@
       <c r="G257" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H257" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111329304','SANDEEP BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
         <v>9110033145</v>
       </c>
@@ -12279,8 +13379,12 @@
       <c r="G258" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H258" t="str">
+        <f t="shared" si="3"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111304866','HARDIK HARDWERE AND BUILDING MAT','VARANASI');</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
         <v>9110033145</v>
       </c>
@@ -12302,8 +13406,12 @@
       <c r="G259" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H259" t="str">
+        <f t="shared" ref="H259:H322" si="4">_xlfn.CONCAT("insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('",A259,"','",C259,"','",D259,"','",E259,"');")</f>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111457192','DEEP SHIKHA BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
         <v>9110033145</v>
       </c>
@@ -12325,8 +13433,12 @@
       <c r="G260" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H260" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9110033145','VISHWANATH PRASAD SATYA CHARAN','VARANASI');</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
         <v>9110033145</v>
       </c>
@@ -12348,8 +13460,12 @@
       <c r="G261" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H261" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111066192','RADHESHYAM GUPTA CEMENT STOCKIST','VARANASI');</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
         <v>9110033145</v>
       </c>
@@ -12371,8 +13487,12 @@
       <c r="G262" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H262" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111358887','PRINCE BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
         <v>9110033145</v>
       </c>
@@ -12394,8 +13514,12 @@
       <c r="G263" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H263" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111062067','ALAKH NARAIN SINGH','VARANASI');</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
         <v>9110033145</v>
       </c>
@@ -12417,8 +13541,12 @@
       <c r="G264" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H264" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111342165','PRADHAN BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
         <v>9110033145</v>
       </c>
@@ -12440,8 +13568,12 @@
       <c r="G265" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H265" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111304871','SAMRAT BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
         <v>9110033145</v>
       </c>
@@ -12463,8 +13595,12 @@
       <c r="G266" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H266" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111329098','YADAV BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
         <v>9110033145</v>
       </c>
@@ -12486,8 +13622,12 @@
       <c r="G267" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H267" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111480495','SURENDRA KUMAR JAISWAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
         <v>9110033145</v>
       </c>
@@ -12509,8 +13649,12 @@
       <c r="G268" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H268" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111225822','SANJAY BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
         <v>9110033145</v>
       </c>
@@ -12532,8 +13676,12 @@
       <c r="G269" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H269" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111147165','RATAN LAL BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
         <v>9110033145</v>
       </c>
@@ -12555,8 +13703,12 @@
       <c r="G270" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H270" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111439453','BHAVANI ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
         <v>9110033145</v>
       </c>
@@ -12578,8 +13730,12 @@
       <c r="G271" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H271" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111468256','SHREE PARAMHANS BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
         <v>9110033145</v>
       </c>
@@ -12601,8 +13757,12 @@
       <c r="G272" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H272" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111328483','SHRI KRISHNA BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
         <v>9110033145</v>
       </c>
@@ -12624,8 +13784,12 @@
       <c r="G273" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H273" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111468257','SHREYANS BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
         <v>9110033145</v>
       </c>
@@ -12647,8 +13811,12 @@
       <c r="G274" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H274" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111203466','SRI RADHESHYAM BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
         <v>9110033145</v>
       </c>
@@ -12670,8 +13838,12 @@
       <c r="G275" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H275" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111414555','GUPTA BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
         <v>9110033145</v>
       </c>
@@ -12693,8 +13865,12 @@
       <c r="G276" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H276" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111443376','SHREE RAM CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
         <v>9110033145</v>
       </c>
@@ -12716,8 +13892,12 @@
       <c r="G277" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H277" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111470081','BABA JI BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
         <v>9110033145</v>
       </c>
@@ -12739,8 +13919,12 @@
       <c r="G278" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H278" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111394845','JANTA BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
         <v>9110033145</v>
       </c>
@@ -12762,8 +13946,12 @@
       <c r="G279" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H279" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111384024','TIRUPATI CONSTRUCTION COMPANY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
         <v>9110033145</v>
       </c>
@@ -12785,8 +13973,12 @@
       <c r="G280" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H280" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111304442','AZAD BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
         <v>9110033145</v>
       </c>
@@ -12808,8 +14000,12 @@
       <c r="G281" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H281" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111488048','ALOK BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="4">
         <v>9110033145</v>
       </c>
@@ -12831,8 +14027,12 @@
       <c r="G282" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H282" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111488056','RAJ ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="4">
         <v>9110033145</v>
       </c>
@@ -12854,8 +14054,12 @@
       <c r="G283" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H283" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111346195','MAA VIDYAVATI ENTERPRISES &amp; SONS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="4">
         <v>9110033145</v>
       </c>
@@ -12877,8 +14081,12 @@
       <c r="G284" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H284" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111437589','KUSH BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="4">
         <v>9110033145</v>
       </c>
@@ -12900,8 +14108,12 @@
       <c r="G285" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H285" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111451895','SARASWATI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="4">
         <v>9110033145</v>
       </c>
@@ -12923,8 +14135,12 @@
       <c r="G286" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H286" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111198403','STAR STEEL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="4">
         <v>9110033145</v>
       </c>
@@ -12946,8 +14162,12 @@
       <c r="G287" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H287" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111360310','SHRI KESHARI BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
         <v>9110033145</v>
       </c>
@@ -12969,8 +14189,12 @@
       <c r="G288" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H288" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111062034','RAMJI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
         <v>9110033145</v>
       </c>
@@ -12992,8 +14216,12 @@
       <c r="G289" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H289" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111470082','D K PRADHAN BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="4">
         <v>9110033145</v>
       </c>
@@ -13015,8 +14243,12 @@
       <c r="G290" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H290" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111454465','GANGA BUILDING MATERIALS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="4">
         <v>9110033145</v>
       </c>
@@ -13038,8 +14270,12 @@
       <c r="G291" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H291" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111152711','BABA BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="4">
         <v>9110033145</v>
       </c>
@@ -13061,8 +14297,12 @@
       <c r="G292" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H292" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111287417','JAI BAJRANG CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
         <v>9110033145</v>
       </c>
@@ -13084,8 +14324,12 @@
       <c r="G293" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H293" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111469057','SHIV SHAKTI PRINCE BUILDING','VARANASI');</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
         <v>9110033145</v>
       </c>
@@ -13107,8 +14351,12 @@
       <c r="G294" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H294" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111447980','JBS TRADING COMPANY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="4">
         <v>9110033145</v>
       </c>
@@ -13130,8 +14378,12 @@
       <c r="G295" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H295" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111405853','SHREE BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
         <v>9110033145</v>
       </c>
@@ -13153,8 +14405,12 @@
       <c r="G296" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H296" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111066202','SHIVAM ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
         <v>9110033145</v>
       </c>
@@ -13176,8 +14432,12 @@
       <c r="G297" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H297" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111066255','PRATAP BUILDERS AND HARDWARE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
         <v>9110033145</v>
       </c>
@@ -13199,8 +14459,12 @@
       <c r="G298" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H298" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111390453','MAA INDRAWATI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
         <v>9110033145</v>
       </c>
@@ -13222,8 +14486,12 @@
       <c r="G299" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H299" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111480494','VIDYARAJ TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
         <v>9110033145</v>
       </c>
@@ -13245,8 +14513,12 @@
       <c r="G300" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H300" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111464767','SWASTIK ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
         <v>9110033145</v>
       </c>
@@ -13268,8 +14540,12 @@
       <c r="G301" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H301" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111388200','VIJAY CONSTRUCTION AND SUPPLY WORKS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
         <v>9110033145</v>
       </c>
@@ -13291,8 +14567,12 @@
       <c r="G302" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H302" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111443377','SATYA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
         <v>9110033145</v>
       </c>
@@ -13314,8 +14594,12 @@
       <c r="G303" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H303" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111304904','AMIT TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
         <v>9110033145</v>
       </c>
@@ -13337,8 +14621,12 @@
       <c r="G304" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H304" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111445760','ANKIT TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
         <v>9110033145</v>
       </c>
@@ -13360,8 +14648,12 @@
       <c r="G305" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H305" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111395235','CHAURASIYA FERTILIZER','VARANASI');</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
         <v>9110033145</v>
       </c>
@@ -13383,8 +14675,12 @@
       <c r="G306" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H306" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111061058','DIXIT BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
         <v>9110033145</v>
       </c>
@@ -13406,8 +14702,12 @@
       <c r="G307" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H307" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111061087','AGRAHARI BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
         <v>9110033145</v>
       </c>
@@ -13429,8 +14729,12 @@
       <c r="G308" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H308" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111149750','GAURAV BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
         <v>9110033145</v>
       </c>
@@ -13452,8 +14756,12 @@
       <c r="G309" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H309" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111066263','DIGVIJAY CEMENT AGENCY','VARANASI');</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
         <v>9110033145</v>
       </c>
@@ -13475,8 +14783,12 @@
       <c r="G310" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H310" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111304897','GAUTAM CEMENT AGENCIE','VARANASI');</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
         <v>9110033145</v>
       </c>
@@ -13498,8 +14810,12 @@
       <c r="G311" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H311" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111304906','GIRDHARI ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
         <v>9110033145</v>
       </c>
@@ -13521,8 +14837,12 @@
       <c r="G312" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H312" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111304903','GOVIND BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
         <v>9110033145</v>
       </c>
@@ -13544,8 +14864,12 @@
       <c r="G313" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H313" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111392095','HARI OM BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" s="4">
         <v>9110033145</v>
       </c>
@@ -13567,8 +14891,12 @@
       <c r="G314" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H314" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111340292','PATEL ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" s="4">
         <v>9110033145</v>
       </c>
@@ -13590,8 +14918,12 @@
       <c r="G315" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H315" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111340688','HEMANT BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" s="4">
         <v>9110033145</v>
       </c>
@@ -13613,8 +14945,12 @@
       <c r="G316" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H316" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111332381','JAI MAA SHARDA STEELS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="4">
         <v>9110033145</v>
       </c>
@@ -13636,8 +14972,12 @@
       <c r="G317" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H317" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111397839','MAA DURGA ENTERPRISES','VARANASI');</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="4">
         <v>9110033145</v>
       </c>
@@ -13659,8 +14999,12 @@
       <c r="G318" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H318" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111328432','PATEL BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="4">
         <v>9110033145</v>
       </c>
@@ -13682,8 +15026,12 @@
       <c r="G319" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H319" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111304895','PANKAJ TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="4">
         <v>9110033145</v>
       </c>
@@ -13705,8 +15053,12 @@
       <c r="G320" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H320" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111480496','MAA LAXMI TRADERS','VARANASI');</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
         <v>9110033145</v>
       </c>
@@ -13728,8 +15080,12 @@
       <c r="G321" s="5" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H321" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111304901','MAHABEER BUILDING MATERIAL','VARANASI');</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="4">
         <v>9110033145</v>
       </c>
@@ -13750,6 +15106,10 @@
       </c>
       <c r="G322" s="5" t="s">
         <v>389</v>
+      </c>
+      <c r="H322" t="str">
+        <f t="shared" si="4"/>
+        <v>insert into odts.dealer_party (dealer_code, party_code, party_company_name, party_address) values ('9110033145','9111489819','MAA VINDHYAVASINI CONSTRUCTION COMP','VARANASI');</v>
       </c>
     </row>
   </sheetData>
@@ -13759,9 +15119,198 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55748DD4-64CD-954A-87CB-D0A48EEA50D6}">
-  <dimension ref="A1"/>
+  <dimension ref="A2:C38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>530</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
